--- a/MC9510_E22.xlsx
+++ b/MC9510_E22.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuvaragan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="297">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -873,12 +873,54 @@
   </si>
   <si>
     <t xml:space="preserve"> SHAFAN A.M.M.</t>
+  </si>
+  <si>
+    <t>I.L.WEERATHUNGA</t>
+  </si>
+  <si>
+    <t>WEERASINGHE D.K.D.</t>
+  </si>
+  <si>
+    <t>P.G.K.G.I. ARIYASINGHE</t>
+  </si>
+  <si>
+    <t>T.D.S.  DE  SILVA</t>
+  </si>
+  <si>
+    <t>NAVEEN  V.VD</t>
+  </si>
+  <si>
+    <t>EKANAYAKA A.J.K.</t>
+  </si>
+  <si>
+    <t>KURKULASURIYA C.M.</t>
+  </si>
+  <si>
+    <t>HERATH H.M.U.C.</t>
+  </si>
+  <si>
+    <t>HETTIARACHCHI  H.P.M.</t>
+  </si>
+  <si>
+    <t>DE MEL L.M.N.H.</t>
+  </si>
+  <si>
+    <t>CHANDRASIRI P.G.P.M.</t>
+  </si>
+  <si>
+    <t>RAJAMINI R.D.D.S.</t>
+  </si>
+  <si>
+    <t>WIJEDASA M.M.D.P.</t>
+  </si>
+  <si>
+    <t>NIDUKANI O.G.H.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -943,6 +985,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Palatino Linotype"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -959,7 +1002,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -979,19 +1022,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1020,7 +1050,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1030,7 +1059,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1056,8 +1084,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1346,7 +1376,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="31.140625" customWidth="1"/>
     <col min="3" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1368,2288 +1398,2566 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="18"/>
+      <c r="C2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7"/>
+      <c r="C3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>87</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
+      <c r="C5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
+      <c r="C6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7"/>
+      <c r="C7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="17">
+        <v>17.39</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>99</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>99</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <v>60</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="17">
+        <v>69.569999999999993</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
+      <c r="C11" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="12">
         <v>88</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="7"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <v>90</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="12">
         <v>70</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="7"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="7"/>
+      <c r="C15" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="7"/>
+      <c r="C16" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="C17" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
+      <c r="C18" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>72</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="7"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>96</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="7"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <v>88</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="7"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="7"/>
+      <c r="C22" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="12">
         <v>97</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="7"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="12">
         <v>99</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="7"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="12">
         <v>58</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="7"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="7"/>
+      <c r="C26" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="17">
+        <v>13.04</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="12">
         <v>96</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="12">
         <v>77</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="7"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="12">
         <v>100</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="7"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="12">
         <v>99</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="7"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="12">
         <v>100</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="7"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="7"/>
+      <c r="C32" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="12">
         <v>74</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="17">
+        <v>65.22</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="12">
         <v>98</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="7"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="17">
+        <v>65.22</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="7"/>
+      <c r="C35" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="7"/>
+      <c r="C36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="7"/>
+      <c r="C37" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="12">
         <v>61</v>
       </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="7"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="12">
         <v>82</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="7"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="12">
         <v>65</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="7"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="17">
+        <v>69.569999999999993</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="12">
         <v>70</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="7"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="7"/>
+      <c r="C42" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="7"/>
+      <c r="C43" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="12">
         <v>79</v>
       </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="7"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="17">
+        <v>65.22</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="12">
         <v>96</v>
       </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="7"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="12">
         <v>96</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="7"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="12">
         <v>96</v>
       </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="7"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="12">
         <v>99</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="7"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="12">
         <v>98</v>
       </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="7"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="12">
         <v>98</v>
       </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="7"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="17">
+        <v>60.870000000000005</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="7"/>
+      <c r="C51" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="12">
         <v>96</v>
       </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="7"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="17">
+        <v>60.870000000000005</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="12">
         <v>65</v>
       </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="7"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="17">
+        <v>52.17</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="12">
         <v>91</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="7"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="12">
         <v>95</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="7"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="7"/>
+      <c r="C56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="7"/>
+      <c r="C57" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="12">
         <v>80</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="7"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="12">
         <v>93</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="7"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="14">
+      <c r="C60" s="12">
         <v>75</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="7"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="7"/>
+      <c r="C61" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="14">
+      <c r="C62" s="12">
         <v>76</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="7"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="17">
+        <v>65.22</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="7"/>
+      <c r="C63" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="14">
+      <c r="C64" s="12">
         <v>85</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="7"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="7"/>
+      <c r="C65" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="7"/>
+      <c r="C66" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="14">
+      <c r="C67" s="12">
         <v>81</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="7"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="7"/>
+      <c r="C68" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="14">
+      <c r="C69" s="12">
         <v>94</v>
       </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="7"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="7"/>
+      <c r="C70" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="14">
+      <c r="C71" s="12">
         <v>78</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="7"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="14">
+      <c r="C72" s="12">
         <v>95</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="7"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="14">
+      <c r="C73" s="12">
         <v>93</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="7"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="14">
+      <c r="C74" s="12">
         <v>96</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="7"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="14">
+      <c r="C75" s="12">
         <v>98</v>
       </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="7"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="14">
+      <c r="C76" s="12">
         <v>100</v>
       </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="7"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="14">
+      <c r="C77" s="12">
         <v>98</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="7"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="7"/>
+      <c r="C78" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="14">
+      <c r="C79" s="12">
         <v>72</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="7"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="4"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="7"/>
+      <c r="C80" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="7"/>
+      <c r="C81" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="14">
+      <c r="C82" s="12">
         <v>74</v>
       </c>
-      <c r="D82" s="4"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="7"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="4"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="7"/>
+      <c r="C83" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="14">
+      <c r="C84" s="12">
         <v>43</v>
       </c>
-      <c r="D84" s="4"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="7"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="4"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="7"/>
+      <c r="C85" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="14">
+      <c r="C86" s="12">
         <v>99</v>
       </c>
-      <c r="D86" s="4"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="7"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="14">
+      <c r="C87" s="12">
         <v>99</v>
       </c>
-      <c r="D87" s="4"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="7"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="14">
+      <c r="C88" s="12">
         <v>85</v>
       </c>
-      <c r="D88" s="4"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="7"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="4"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="7"/>
+      <c r="C89" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="4"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="7"/>
+      <c r="C90" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="14">
+      <c r="C91" s="12">
         <v>93</v>
       </c>
-      <c r="D91" s="4"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="7"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="4"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="7"/>
+      <c r="C92" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="14">
+      <c r="C93" s="12">
         <v>99</v>
       </c>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="7"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="14">
+      <c r="C94" s="12">
         <v>70</v>
       </c>
-      <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="7"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="17">
+        <v>95.65</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="14">
+      <c r="C95" s="12">
         <v>90</v>
       </c>
-      <c r="D95" s="4"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="7"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="14">
+      <c r="C96" s="12">
         <v>82</v>
       </c>
-      <c r="D96" s="4"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="7"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="17">
+        <v>69.569999999999993</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="14">
+      <c r="C97" s="12">
         <v>55</v>
       </c>
-      <c r="D97" s="4"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="7"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="17"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="14">
+      <c r="C98" s="12">
         <v>100</v>
       </c>
-      <c r="D98" s="4"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="7"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="4"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="7"/>
+      <c r="C99" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="14">
+      <c r="C100" s="12">
         <v>93</v>
       </c>
-      <c r="D100" s="4"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="7"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="14">
+      <c r="C101" s="12">
         <v>81</v>
       </c>
-      <c r="D101" s="4"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="7"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="17">
+        <v>76.19</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="14">
+      <c r="C102" s="12">
         <v>71</v>
       </c>
-      <c r="D102" s="4"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="7"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B103" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="4"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="7"/>
+      <c r="C103" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B104" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="14">
+      <c r="C104" s="12">
         <v>85</v>
       </c>
-      <c r="D104" s="4"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="7"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="17">
+        <v>78.259999999999991</v>
+      </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B105" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="4"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="7"/>
+      <c r="C105" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+      <c r="A106" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="14">
+      <c r="C106" s="12">
         <v>71</v>
       </c>
-      <c r="D106" s="4"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="7"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="17">
+        <v>82.61</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="14">
+      <c r="C107" s="12">
         <v>98</v>
       </c>
-      <c r="D107" s="4"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="7"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="14">
+      <c r="C108" s="12">
         <v>83</v>
       </c>
-      <c r="D108" s="4"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="7"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B109" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="14">
+      <c r="C109" s="12">
         <v>73</v>
       </c>
-      <c r="D109" s="4"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="7"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="17">
+        <v>86.960000000000008</v>
+      </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B110" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="4"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="7"/>
+      <c r="C110" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="3"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B111" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="14">
+      <c r="C111" s="12">
         <v>99</v>
       </c>
-      <c r="D111" s="4"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="7"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B112" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="4"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="7"/>
+      <c r="C112" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="17">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B113" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="14">
+      <c r="C113" s="12">
         <v>89</v>
       </c>
-      <c r="D113" s="4"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="7"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="17">
+        <v>91.3</v>
+      </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B114" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C114" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="4"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="7"/>
+      <c r="C114" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="3"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B115" s="10"/>
-      <c r="C115" s="14">
+      <c r="B115" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C115" s="12">
         <v>64</v>
       </c>
-      <c r="D115" s="4"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="7"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="17"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B116" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="4"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="7"/>
+      <c r="C116" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="3"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="17">
+        <v>8.6999999999999993</v>
+      </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B117" s="10"/>
-      <c r="C117" s="14">
+      <c r="B117" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C117" s="12">
         <v>61</v>
       </c>
-      <c r="D117" s="4"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="7"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="17"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B118" s="10"/>
-      <c r="C118" s="14">
+      <c r="B118" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C118" s="12">
         <v>75</v>
       </c>
-      <c r="D118" s="4"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="7"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="17">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B119" s="10"/>
-      <c r="C119" s="14">
+      <c r="B119" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C119" s="12">
         <v>49</v>
       </c>
-      <c r="D119" s="4"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="7"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="17">
+        <v>14.29</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B120" s="10"/>
-      <c r="C120" s="14">
+      <c r="B120" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C120" s="12">
         <v>59</v>
       </c>
-      <c r="D120" s="4"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="7"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="17"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B121" s="10"/>
-      <c r="C121" s="14">
+      <c r="B121" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C121" s="12">
         <v>47</v>
       </c>
-      <c r="D121" s="4"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="7"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="17"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C122" s="14">
+      <c r="C122" s="12">
         <v>61</v>
       </c>
-      <c r="D122" s="4"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="7"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="17">
+        <v>9.5200000000000014</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="4"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="7"/>
+      <c r="C123" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="3"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="17"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B124" s="10"/>
-      <c r="C124" s="14">
+      <c r="B124" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C124" s="12">
         <v>75</v>
       </c>
-      <c r="D124" s="4"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="7"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="17"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B125" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C125" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="4"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="7"/>
+      <c r="C125" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="3"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="17"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="10"/>
-      <c r="C126" s="14">
+      <c r="B126" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C126" s="12">
         <v>37</v>
       </c>
-      <c r="D126" s="4"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="7"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="17"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B127" s="10"/>
-      <c r="C127" s="14">
+      <c r="B127" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C127" s="12">
         <v>79</v>
       </c>
-      <c r="D127" s="4"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="7"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="17">
+        <v>14.29</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B128" s="10"/>
-      <c r="C128" s="14">
+      <c r="B128" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C128" s="12">
         <v>62</v>
       </c>
-      <c r="D128" s="4"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="7"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="17"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B129" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C129" s="14">
+      <c r="C129" s="12">
         <v>67</v>
       </c>
-      <c r="D129" s="4"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="7"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="17">
+        <v>69.569999999999993</v>
+      </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B130" s="10"/>
-      <c r="C130" s="14">
+      <c r="B130" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" s="12">
         <v>99</v>
       </c>
-      <c r="D130" s="4"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="7"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="17">
+        <v>19.05</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B131" s="10"/>
-      <c r="C131" s="14">
+      <c r="B131" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" s="12">
         <v>85</v>
       </c>
-      <c r="D131" s="4"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="7"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="17">
+        <v>9.5200000000000014</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B132" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C132" s="14">
+      <c r="C132" s="12">
         <v>48</v>
       </c>
-      <c r="D132" s="4"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="7"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="17">
+        <v>71.430000000000007</v>
+      </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="13" t="s">
+      <c r="A133" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B133" s="10"/>
-      <c r="C133" s="14">
+      <c r="B133" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C133" s="12">
         <v>55</v>
       </c>
-      <c r="D133" s="4"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="7"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="17"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C134" s="14">
+      <c r="C134" s="12">
         <v>72</v>
       </c>
-      <c r="D134" s="4"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="7"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="17">
+        <v>73.91</v>
+      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B135" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C135" s="14">
+      <c r="C135" s="12">
         <v>77</v>
       </c>
-      <c r="D135" s="4"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="7"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="17">
+        <v>14.29</v>
+      </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B136" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C136" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D136" s="4"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="7"/>
+      <c r="C136" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="3"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="17"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B137" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C137" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D137" s="4"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="5"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="7"/>
+      <c r="C137" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="3"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="17"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B138" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C138" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D138" s="4"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="5"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="7"/>
+      <c r="C138" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="3"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="17"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B139" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C139" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="4"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="7"/>
+      <c r="C139" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="3"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="17"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B140" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C140" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="4"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="7"/>
+      <c r="C140" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="17"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B141" s="10"/>
-      <c r="C141" s="14">
+      <c r="B141" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" s="12">
         <v>59</v>
       </c>
-      <c r="D141" s="4"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="5"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="7"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="17"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="13" t="s">
+      <c r="A142" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B142" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C142" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="4"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="7"/>
+      <c r="C142" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="3"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="17"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="13" t="s">
+      <c r="A143" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B143" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C143" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="4"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="7"/>
+      <c r="C143" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="3"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="17">
+        <v>17.39</v>
+      </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C144" s="14">
+      <c r="C144" s="12">
         <v>48</v>
       </c>
-      <c r="D144" s="4"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="7"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="17">
+        <v>39.129999999999995</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B145" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C145" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D145" s="15"/>
-      <c r="E145" s="15"/>
-      <c r="F145" s="15"/>
-      <c r="G145" s="15"/>
-      <c r="H145" s="15"/>
+      <c r="C145" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
+      <c r="H145" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MC9510_E22.xlsx
+++ b/MC9510_E22.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B409D0-F763-45C1-BA17-310C41E9A481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -23,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="297">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -928,9 +927,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1004,7 +1003,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1040,21 +1039,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1063,9 +1108,6 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1089,14 +1131,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1368,7 +1422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -1414,11 +1468,13 @@
       <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="18">
+      <c r="D2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1429,14 +1485,16 @@
       <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="18">
+      <c r="C3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="17">
         <v>12.120000000000001</v>
       </c>
     </row>
@@ -1447,14 +1505,16 @@
       <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>87</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="18">
+      <c r="D4" s="19">
+        <v>86</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -1465,14 +1525,16 @@
       <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="18">
+      <c r="C5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1483,14 +1545,16 @@
       <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="18">
+      <c r="C6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1501,122 +1565,136 @@
       <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="18">
+      <c r="C7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="17">
         <v>18.18</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>99</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="18">
+      <c r="D8" s="19">
+        <v>80</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="17">
         <v>87.88</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>99</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="18">
+      <c r="D9" s="19">
+        <v>77</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="17">
         <v>90.91</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>60</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="18">
+      <c r="D10" s="19">
+        <v>55</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="17">
         <v>72.72999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="18">
+      <c r="C11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="17">
         <v>9.09</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>88</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="18">
+      <c r="D12" s="19">
+        <v>75.5</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>90</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="18">
+      <c r="D13" s="19">
+        <v>69</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="17">
         <v>96.97</v>
       </c>
     </row>
@@ -1627,14 +1705,16 @@
       <c r="B14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>70</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="18">
+      <c r="D14" s="20">
+        <v>78</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -1645,14 +1725,16 @@
       <c r="B15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="18">
+      <c r="C15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1663,14 +1745,16 @@
       <c r="B16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="18">
+      <c r="C16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1681,50 +1765,56 @@
       <c r="B17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="18">
+      <c r="C17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="18">
+      <c r="C18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="17">
         <v>9.09</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>72</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="18">
+      <c r="D19" s="19">
+        <v>48</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1735,14 +1825,16 @@
       <c r="B20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>96</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="18">
+      <c r="D20" s="19">
+        <v>87</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -1753,14 +1845,16 @@
       <c r="B21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>88</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="18">
+      <c r="D21" s="19">
+        <v>51</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -1771,14 +1865,16 @@
       <c r="B22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="18">
+      <c r="C22" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1789,32 +1885,36 @@
       <c r="B23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>97</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="18">
+      <c r="D23" s="19">
+        <v>91</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="17">
         <v>93.94</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <v>99</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="18">
+      <c r="D24" s="19">
+        <v>92</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1825,14 +1925,16 @@
       <c r="B25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <v>58</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="18">
+      <c r="D25" s="19">
+        <v>74</v>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -1843,14 +1945,16 @@
       <c r="B26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="18">
+      <c r="C26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="17">
         <v>12.120000000000001</v>
       </c>
     </row>
@@ -1861,14 +1965,16 @@
       <c r="B27" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <v>96</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="18">
+      <c r="D27" s="19">
+        <v>82</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -1879,50 +1985,56 @@
       <c r="B28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <v>77</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="18">
+      <c r="D28" s="19">
+        <v>66</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="17">
         <v>90.91</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <v>100</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="18">
+      <c r="D29" s="19">
+        <v>73.5</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="17">
         <v>87.88</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <v>99</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="18">
+      <c r="D30" s="19">
+        <v>82</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="17">
         <v>93.94</v>
       </c>
     </row>
@@ -1933,14 +2045,16 @@
       <c r="B31" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <v>100</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="18">
+      <c r="D31" s="19">
+        <v>80</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1954,11 +2068,13 @@
       <c r="C32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="18">
+      <c r="D32" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1969,14 +2085,16 @@
       <c r="B33" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <v>74</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="18">
+      <c r="D33" s="19">
+        <v>71</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
@@ -1987,14 +2105,16 @@
       <c r="B34" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <v>98</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="18">
+      <c r="D34" s="19">
+        <v>73</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2008,11 +2128,13 @@
       <c r="C35" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="18">
+      <c r="D35" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2026,11 +2148,13 @@
       <c r="C36" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="18">
+      <c r="D36" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2044,11 +2168,13 @@
       <c r="C37" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="18">
+      <c r="D37" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2059,14 +2185,16 @@
       <c r="B38" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="11">
         <v>61</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="18">
+      <c r="D38" s="19">
+        <v>78</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2077,14 +2205,16 @@
       <c r="B39" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="11">
         <v>82</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="18">
+      <c r="D39" s="19">
+        <v>67</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2095,14 +2225,16 @@
       <c r="B40" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="11">
         <v>65</v>
       </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="18">
+      <c r="D40" s="19">
+        <v>43</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2113,14 +2245,16 @@
       <c r="B41" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="11">
         <v>70</v>
       </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="18">
+      <c r="D41" s="19">
+        <v>60</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2134,11 +2268,13 @@
       <c r="C42" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="18">
+      <c r="D42" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2152,29 +2288,33 @@
       <c r="C43" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="18">
+      <c r="D43" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="11">
         <v>79</v>
       </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="18">
+      <c r="D44" s="19">
+        <v>76</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
@@ -2185,14 +2325,16 @@
       <c r="B45" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <v>96</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="18">
+      <c r="D45" s="19">
+        <v>73</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2203,14 +2345,16 @@
       <c r="B46" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
         <v>96</v>
       </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="18">
+      <c r="D46" s="19">
+        <v>85</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2221,14 +2365,16 @@
       <c r="B47" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <v>96</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="18">
+      <c r="D47" s="19">
+        <v>87</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="17">
         <v>96.97</v>
       </c>
     </row>
@@ -2239,14 +2385,16 @@
       <c r="B48" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <v>99</v>
       </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="18">
+      <c r="D48" s="19">
+        <v>63</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2257,14 +2405,16 @@
       <c r="B49" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="11">
         <v>98</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="18">
+      <c r="D49" s="19">
+        <v>80</v>
+      </c>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2275,32 +2425,36 @@
       <c r="B50" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="11">
         <v>98</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="18">
+      <c r="D50" s="19">
+        <v>79</v>
+      </c>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="17">
         <v>66.67</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="18">
+      <c r="D51" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2311,14 +2465,16 @@
       <c r="B52" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="11">
         <v>96</v>
       </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="18">
+      <c r="D52" s="19">
+        <v>86</v>
+      </c>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="17">
         <v>66.67</v>
       </c>
     </row>
@@ -2329,14 +2485,16 @@
       <c r="B53" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <v>65</v>
       </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="18">
+      <c r="D53" s="19">
+        <v>84</v>
+      </c>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="17">
         <v>63.639999999999993</v>
       </c>
     </row>
@@ -2347,14 +2505,16 @@
       <c r="B54" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="11">
         <v>91</v>
       </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="18">
+      <c r="D54" s="21">
+        <v>74</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="17">
         <v>96.97</v>
       </c>
     </row>
@@ -2365,14 +2525,16 @@
       <c r="B55" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="11">
         <v>95</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="18">
+      <c r="D55" s="19">
+        <v>94.5</v>
+      </c>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2386,11 +2548,13 @@
       <c r="C56" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="18">
+      <c r="D56" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="17">
         <v>9.09</v>
       </c>
     </row>
@@ -2404,29 +2568,33 @@
       <c r="C57" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="18">
+      <c r="D57" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="11">
         <v>80</v>
       </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="18">
+      <c r="D58" s="19">
+        <v>84</v>
+      </c>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2437,14 +2605,16 @@
       <c r="B59" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="11">
         <v>93</v>
       </c>
-      <c r="D59" s="9"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="18">
+      <c r="D59" s="19">
+        <v>80</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2455,32 +2625,36 @@
       <c r="B60" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="11">
         <v>75</v>
       </c>
-      <c r="D60" s="9"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="18">
+      <c r="D60" s="19">
+        <v>79</v>
+      </c>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="17">
         <v>87.88</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="14" t="s">
         <v>128</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="9"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="18">
+      <c r="D61" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2491,50 +2665,56 @@
       <c r="B62" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="11">
         <v>76</v>
       </c>
-      <c r="D62" s="9"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="18">
+      <c r="D62" s="19">
+        <v>66.5</v>
+      </c>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="14" t="s">
         <v>132</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="9"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="18">
+      <c r="D63" s="19">
+        <v>40</v>
+      </c>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <v>85</v>
       </c>
-      <c r="D64" s="9"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="18">
+      <c r="D64" s="19">
+        <v>55</v>
+      </c>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -2548,11 +2728,13 @@
       <c r="C65" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="9"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="18">
+      <c r="D65" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="17">
         <v>9.09</v>
       </c>
     </row>
@@ -2566,29 +2748,33 @@
       <c r="C66" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="9"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="18">
+      <c r="D66" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="11">
         <v>81</v>
       </c>
-      <c r="D67" s="9"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="18">
+      <c r="D67" s="19">
+        <v>74</v>
+      </c>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2602,11 +2788,13 @@
       <c r="C68" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="9"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="18">
+      <c r="D68" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="17">
         <v>9.09</v>
       </c>
     </row>
@@ -2617,14 +2805,16 @@
       <c r="B69" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <v>94</v>
       </c>
-      <c r="D69" s="9"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="18">
+      <c r="D69" s="19">
+        <v>85</v>
+      </c>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2638,11 +2828,13 @@
       <c r="C70" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="9"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="18">
+      <c r="D70" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2653,14 +2845,16 @@
       <c r="B71" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="11">
         <v>78</v>
       </c>
-      <c r="D71" s="9"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="18">
+      <c r="D71" s="19">
+        <v>64</v>
+      </c>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -2671,14 +2865,16 @@
       <c r="B72" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="11">
         <v>95</v>
       </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="18">
+      <c r="D72" s="19">
+        <v>86</v>
+      </c>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2689,14 +2885,16 @@
       <c r="B73" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="11">
         <v>93</v>
       </c>
-      <c r="D73" s="9"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="18">
+      <c r="D73" s="19">
+        <v>79.5</v>
+      </c>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="17">
         <v>72.72999999999999</v>
       </c>
     </row>
@@ -2707,14 +2905,16 @@
       <c r="B74" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="11">
         <v>96</v>
       </c>
-      <c r="D74" s="9"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="18">
+      <c r="D74" s="19">
+        <v>95</v>
+      </c>
+      <c r="E74" s="15"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="17">
         <v>93.94</v>
       </c>
     </row>
@@ -2725,14 +2925,16 @@
       <c r="B75" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="11">
         <v>98</v>
       </c>
-      <c r="D75" s="9"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="18">
+      <c r="D75" s="19">
+        <v>94</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2743,14 +2945,16 @@
       <c r="B76" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="11">
         <v>100</v>
       </c>
-      <c r="D76" s="9"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="18">
+      <c r="D76" s="19">
+        <v>83</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -2761,14 +2965,16 @@
       <c r="B77" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="11">
         <v>98</v>
       </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="18">
+      <c r="D77" s="19">
+        <v>70</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2782,11 +2988,13 @@
       <c r="C78" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="18">
+      <c r="D78" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2797,14 +3005,16 @@
       <c r="B79" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="11">
         <v>72</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="18">
+      <c r="D79" s="19">
+        <v>84</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2818,11 +3028,13 @@
       <c r="C80" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="18">
+      <c r="D80" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2836,11 +3048,13 @@
       <c r="C81" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D81" s="9"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="18">
+      <c r="D81" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="17">
         <v>3.0300000000000002</v>
       </c>
     </row>
@@ -2851,14 +3065,16 @@
       <c r="B82" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="11">
         <v>74</v>
       </c>
-      <c r="D82" s="9"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="18">
+      <c r="D82" s="19">
+        <v>79</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2872,11 +3088,13 @@
       <c r="C83" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D83" s="9"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="18">
+      <c r="D83" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2887,14 +3105,16 @@
       <c r="B84" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="11">
         <v>43</v>
       </c>
-      <c r="D84" s="9"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="18">
+      <c r="D84" s="19">
+        <v>69</v>
+      </c>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="10"/>
+      <c r="H84" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2908,11 +3128,13 @@
       <c r="C85" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="9"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="18">
+      <c r="D85" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2923,14 +3145,16 @@
       <c r="B86" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="11">
         <v>99</v>
       </c>
-      <c r="D86" s="9"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="18">
+      <c r="D86" s="19">
+        <v>81</v>
+      </c>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -2941,14 +3165,16 @@
       <c r="B87" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="11">
         <v>99</v>
       </c>
-      <c r="D87" s="9"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="18">
+      <c r="D87" s="19">
+        <v>83</v>
+      </c>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2959,14 +3185,16 @@
       <c r="B88" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="11">
         <v>85</v>
       </c>
-      <c r="D88" s="9"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="18">
+      <c r="D88" s="19">
+        <v>56</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2980,11 +3208,13 @@
       <c r="C89" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="9"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="18">
+      <c r="D89" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2998,11 +3228,13 @@
       <c r="C90" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D90" s="9"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="18">
+      <c r="D90" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="10"/>
+      <c r="H90" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3013,14 +3245,16 @@
       <c r="B91" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="11">
         <v>93</v>
       </c>
-      <c r="D91" s="9"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="18">
+      <c r="D91" s="19">
+        <v>67</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -3034,11 +3268,13 @@
       <c r="C92" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D92" s="9"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="18">
+      <c r="D92" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="17">
         <v>9.09</v>
       </c>
     </row>
@@ -3049,14 +3285,16 @@
       <c r="B93" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="11">
         <v>99</v>
       </c>
-      <c r="D93" s="9"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="18">
+      <c r="D93" s="19">
+        <v>84</v>
+      </c>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3067,14 +3305,16 @@
       <c r="B94" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="12">
+      <c r="C94" s="11">
         <v>70</v>
       </c>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="18">
+      <c r="D94" s="19">
+        <v>90</v>
+      </c>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="17">
         <v>96.97</v>
       </c>
     </row>
@@ -3085,14 +3325,16 @@
       <c r="B95" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="11">
         <v>90</v>
       </c>
-      <c r="D95" s="9"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="11"/>
-      <c r="H95" s="18">
+      <c r="D95" s="19">
+        <v>79</v>
+      </c>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="17">
         <v>90.91</v>
       </c>
     </row>
@@ -3103,14 +3345,16 @@
       <c r="B96" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="11">
         <v>82</v>
       </c>
-      <c r="D96" s="9"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="18">
+      <c r="D96" s="19">
+        <v>59.5</v>
+      </c>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -3121,14 +3365,16 @@
       <c r="B97" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="11">
         <v>55</v>
       </c>
-      <c r="D97" s="9"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="18"/>
+      <c r="D97" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="17"/>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="6" t="s">
@@ -3137,14 +3383,16 @@
       <c r="B98" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="12">
+      <c r="C98" s="11">
         <v>100</v>
       </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="18">
+      <c r="D98" s="19">
+        <v>89</v>
+      </c>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3158,11 +3406,13 @@
       <c r="C99" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D99" s="9"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="11"/>
-      <c r="H99" s="18">
+      <c r="D99" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3173,14 +3423,16 @@
       <c r="B100" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="12">
+      <c r="C100" s="11">
         <v>93</v>
       </c>
-      <c r="D100" s="9"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="18">
+      <c r="D100" s="19">
+        <v>86</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3191,32 +3443,36 @@
       <c r="B101" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101" s="11">
         <v>81</v>
       </c>
-      <c r="D101" s="9"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="11"/>
-      <c r="H101" s="18">
+      <c r="D101" s="19">
+        <v>71</v>
+      </c>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="17">
         <v>83.33</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C102" s="11">
         <v>71</v>
       </c>
-      <c r="D102" s="9"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="18">
+      <c r="D102" s="19">
+        <v>55</v>
+      </c>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="10"/>
+      <c r="H102" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -3230,11 +3486,13 @@
       <c r="C103" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="9"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="11"/>
-      <c r="H103" s="18">
+      <c r="D103" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="15"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="10"/>
+      <c r="H103" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3245,14 +3503,16 @@
       <c r="B104" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104" s="11">
         <v>85</v>
       </c>
-      <c r="D104" s="9"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="11"/>
-      <c r="H104" s="18">
+      <c r="D104" s="19">
+        <v>88</v>
+      </c>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="10"/>
+      <c r="H104" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3266,11 +3526,13 @@
       <c r="C105" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D105" s="9"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="18">
+      <c r="D105" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="10"/>
+      <c r="H105" s="17">
         <v>3.0300000000000002</v>
       </c>
     </row>
@@ -3281,50 +3543,56 @@
       <c r="B106" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="12">
+      <c r="C106" s="11">
         <v>71</v>
       </c>
-      <c r="D106" s="9"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="11"/>
-      <c r="H106" s="18">
+      <c r="D106" s="19">
+        <v>65</v>
+      </c>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="10"/>
+      <c r="H106" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="12">
+      <c r="C107" s="11">
         <v>98</v>
       </c>
-      <c r="D107" s="9"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="11"/>
-      <c r="H107" s="18">
+      <c r="D107" s="19">
+        <v>55</v>
+      </c>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="10"/>
+      <c r="H107" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="12">
+      <c r="C108" s="11">
         <v>83</v>
       </c>
-      <c r="D108" s="9"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="18">
+      <c r="D108" s="19">
+        <v>91</v>
+      </c>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="10"/>
+      <c r="H108" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -3335,14 +3603,16 @@
       <c r="B109" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109" s="11">
         <v>73</v>
       </c>
-      <c r="D109" s="9"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="18">
+      <c r="D109" s="19">
+        <v>65</v>
+      </c>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="10"/>
+      <c r="H109" s="17">
         <v>87.88</v>
       </c>
     </row>
@@ -3356,11 +3626,13 @@
       <c r="C110" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D110" s="9"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="11"/>
-      <c r="H110" s="18">
+      <c r="D110" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="10"/>
+      <c r="H110" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3371,19 +3643,21 @@
       <c r="B111" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="12">
+      <c r="C111" s="11">
         <v>99</v>
       </c>
-      <c r="D111" s="9"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="18">
+      <c r="D111" s="19">
+        <v>81</v>
+      </c>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="10"/>
+      <c r="H111" s="17">
         <v>90.91</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="13" t="s">
         <v>229</v>
       </c>
       <c r="B112" s="7" t="s">
@@ -3392,34 +3666,38 @@
       <c r="C112" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D112" s="9"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="11"/>
-      <c r="H112" s="18">
+      <c r="D112" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="10"/>
+      <c r="H112" s="17">
         <v>3.0300000000000002</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="13" t="s">
         <v>231</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113" s="11">
         <v>89</v>
       </c>
-      <c r="D113" s="9"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="11"/>
-      <c r="H113" s="18">
+      <c r="D113" s="19">
+        <v>87</v>
+      </c>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="10"/>
+      <c r="H113" s="17">
         <v>90.91</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="13" t="s">
         <v>233</v>
       </c>
       <c r="B114" s="7" t="s">
@@ -3428,32 +3706,36 @@
       <c r="C114" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D114" s="9"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="11"/>
-      <c r="H114" s="18">
+      <c r="D114" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="10"/>
+      <c r="H114" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="13" t="s">
         <v>236</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C115" s="12">
+      <c r="C115" s="11">
         <v>64</v>
       </c>
-      <c r="D115" s="9"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="18"/>
+      <c r="D115" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="10"/>
+      <c r="H115" s="17"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="13" t="s">
         <v>235</v>
       </c>
       <c r="B116" s="7" t="s">
@@ -3462,124 +3744,138 @@
       <c r="C116" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D116" s="9"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="18">
+      <c r="D116" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="10"/>
+      <c r="H116" s="17">
         <v>12.120000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="13" t="s">
         <v>241</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C117" s="12">
+      <c r="C117" s="11">
         <v>61</v>
       </c>
-      <c r="D117" s="9"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="10"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="18">
+      <c r="D117" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="10"/>
+      <c r="H117" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="14" t="s">
+      <c r="A118" s="13" t="s">
         <v>244</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C118" s="12">
+      <c r="C118" s="11">
         <v>75</v>
       </c>
-      <c r="D118" s="9"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="10"/>
-      <c r="G118" s="11"/>
-      <c r="H118" s="18">
+      <c r="D118" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="10"/>
+      <c r="H118" s="17">
         <v>30.3</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="13" t="s">
         <v>247</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C119" s="12">
+      <c r="C119" s="11">
         <v>49</v>
       </c>
-      <c r="D119" s="9"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="10"/>
-      <c r="G119" s="11"/>
-      <c r="H119" s="18">
+      <c r="D119" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
+      <c r="G119" s="10"/>
+      <c r="H119" s="17">
         <v>15.15</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="14" t="s">
+      <c r="A120" s="13" t="s">
         <v>250</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C120" s="12">
+      <c r="C120" s="11">
         <v>59</v>
       </c>
-      <c r="D120" s="9"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="10"/>
-      <c r="G120" s="11"/>
-      <c r="H120" s="18">
+      <c r="D120" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="9"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="10"/>
+      <c r="H120" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="13" t="s">
         <v>253</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C121" s="12">
+      <c r="C121" s="11">
         <v>47</v>
       </c>
-      <c r="D121" s="9"/>
-      <c r="E121" s="10"/>
-      <c r="F121" s="10"/>
-      <c r="G121" s="11"/>
-      <c r="H121" s="18">
+      <c r="D121" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="10"/>
+      <c r="H121" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="14" t="s">
+      <c r="A122" s="13" t="s">
         <v>256</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C122" s="12">
+      <c r="C122" s="11">
         <v>61</v>
       </c>
-      <c r="D122" s="9"/>
-      <c r="E122" s="10"/>
-      <c r="F122" s="10"/>
-      <c r="G122" s="11"/>
-      <c r="H122" s="18">
+      <c r="D122" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="10"/>
+      <c r="H122" s="17">
         <v>9.09</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="13" t="s">
         <v>238</v>
       </c>
       <c r="B123" s="7" t="s">
@@ -3588,34 +3884,38 @@
       <c r="C123" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D123" s="9"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="10"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="18">
+      <c r="D123" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="10"/>
+      <c r="H123" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="13" t="s">
         <v>261</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C124" s="12">
+      <c r="C124" s="11">
         <v>75</v>
       </c>
-      <c r="D124" s="9"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10"/>
-      <c r="G124" s="11"/>
-      <c r="H124" s="18">
+      <c r="D124" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="10"/>
+      <c r="H124" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="14" t="s">
+      <c r="A125" s="13" t="s">
         <v>240</v>
       </c>
       <c r="B125" s="7" t="s">
@@ -3624,196 +3924,218 @@
       <c r="C125" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D125" s="9"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="10"/>
-      <c r="G125" s="11"/>
-      <c r="H125" s="18">
+      <c r="D125" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="10"/>
+      <c r="H125" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="14" t="s">
+      <c r="A126" s="13" t="s">
         <v>266</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C126" s="12">
+      <c r="C126" s="11">
         <v>37</v>
       </c>
-      <c r="D126" s="9"/>
-      <c r="E126" s="10"/>
-      <c r="F126" s="10"/>
-      <c r="G126" s="11"/>
-      <c r="H126" s="18">
+      <c r="D126" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="9"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="10"/>
+      <c r="H126" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="13" t="s">
         <v>269</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="C127" s="12">
+      <c r="C127" s="11">
         <v>79</v>
       </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="10"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="18">
+      <c r="D127" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="17">
         <v>15.15</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="14" t="s">
+      <c r="A128" s="13" t="s">
         <v>272</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="12">
+      <c r="C128" s="11">
         <v>62</v>
       </c>
-      <c r="D128" s="9"/>
-      <c r="E128" s="10"/>
-      <c r="F128" s="10"/>
-      <c r="G128" s="11"/>
-      <c r="H128" s="18">
+      <c r="D128" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="10"/>
+      <c r="H128" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="14" t="s">
+      <c r="A129" s="13" t="s">
         <v>243</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C129" s="12">
+      <c r="C129" s="11">
         <v>67</v>
       </c>
-      <c r="D129" s="9"/>
-      <c r="E129" s="10"/>
-      <c r="F129" s="10"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="18">
+      <c r="D129" s="19">
+        <v>59</v>
+      </c>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="10"/>
+      <c r="H129" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="13" t="s">
         <v>276</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C130" s="12">
+      <c r="C130" s="11">
         <v>99</v>
       </c>
-      <c r="D130" s="9"/>
-      <c r="E130" s="10"/>
-      <c r="F130" s="10"/>
-      <c r="G130" s="11"/>
-      <c r="H130" s="18">
+      <c r="D130" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="10"/>
+      <c r="H130" s="17">
         <v>21.21</v>
       </c>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="13" t="s">
         <v>278</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C131" s="12">
+      <c r="C131" s="11">
         <v>85</v>
       </c>
-      <c r="D131" s="9"/>
-      <c r="E131" s="10"/>
-      <c r="F131" s="10"/>
-      <c r="G131" s="11"/>
-      <c r="H131" s="18">
+      <c r="D131" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="17">
         <v>9.09</v>
       </c>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="13" t="s">
         <v>274</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C132" s="12">
+      <c r="C132" s="11">
         <v>48</v>
       </c>
-      <c r="D132" s="9"/>
-      <c r="E132" s="10"/>
-      <c r="F132" s="10"/>
-      <c r="G132" s="11"/>
-      <c r="H132" s="18">
+      <c r="D132" s="19">
+        <v>31</v>
+      </c>
+      <c r="E132" s="9"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="10"/>
+      <c r="H132" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="C133" s="12">
+      <c r="C133" s="11">
         <v>55</v>
       </c>
-      <c r="D133" s="9"/>
-      <c r="E133" s="10"/>
-      <c r="F133" s="10"/>
-      <c r="G133" s="11"/>
-      <c r="H133" s="18">
+      <c r="D133" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" s="9"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="10"/>
+      <c r="H133" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="13" t="s">
         <v>246</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C134" s="12">
+      <c r="C134" s="11">
         <v>72</v>
       </c>
-      <c r="D134" s="9"/>
-      <c r="E134" s="10"/>
-      <c r="F134" s="10"/>
-      <c r="G134" s="11"/>
-      <c r="H134" s="18">
+      <c r="D134" s="19">
+        <v>54</v>
+      </c>
+      <c r="E134" s="9"/>
+      <c r="F134" s="9"/>
+      <c r="G134" s="10"/>
+      <c r="H134" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="14" t="s">
+      <c r="A135" s="13" t="s">
         <v>284</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C135" s="12">
+      <c r="C135" s="11">
         <v>77</v>
       </c>
-      <c r="D135" s="9"/>
-      <c r="E135" s="10"/>
-      <c r="F135" s="10"/>
-      <c r="G135" s="11"/>
-      <c r="H135" s="18">
+      <c r="D135" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="9"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="10"/>
+      <c r="H135" s="17">
         <v>15.15</v>
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="13" t="s">
         <v>249</v>
       </c>
       <c r="B136" s="7" t="s">
@@ -3822,16 +4144,18 @@
       <c r="C136" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D136" s="9"/>
-      <c r="E136" s="10"/>
-      <c r="F136" s="10"/>
-      <c r="G136" s="11"/>
-      <c r="H136" s="18">
+      <c r="D136" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E136" s="9"/>
+      <c r="F136" s="9"/>
+      <c r="G136" s="10"/>
+      <c r="H136" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="13" t="s">
         <v>252</v>
       </c>
       <c r="B137" s="7" t="s">
@@ -3840,16 +4164,18 @@
       <c r="C137" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D137" s="9"/>
-      <c r="E137" s="10"/>
-      <c r="F137" s="10"/>
-      <c r="G137" s="11"/>
-      <c r="H137" s="18">
+      <c r="D137" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" s="9"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="10"/>
+      <c r="H137" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="13" t="s">
         <v>255</v>
       </c>
       <c r="B138" s="7" t="s">
@@ -3858,16 +4184,18 @@
       <c r="C138" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D138" s="9"/>
-      <c r="E138" s="10"/>
-      <c r="F138" s="10"/>
-      <c r="G138" s="11"/>
-      <c r="H138" s="18">
+      <c r="D138" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="10"/>
+      <c r="H138" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="14" t="s">
+      <c r="A139" s="13" t="s">
         <v>258</v>
       </c>
       <c r="B139" s="7" t="s">
@@ -3876,16 +4204,18 @@
       <c r="C139" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D139" s="9"/>
-      <c r="E139" s="10"/>
-      <c r="F139" s="10"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="18">
+      <c r="D139" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="9"/>
+      <c r="F139" s="9"/>
+      <c r="G139" s="10"/>
+      <c r="H139" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="13" t="s">
         <v>260</v>
       </c>
       <c r="B140" s="7" t="s">
@@ -3894,34 +4224,38 @@
       <c r="C140" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D140" s="9"/>
-      <c r="E140" s="10"/>
-      <c r="F140" s="10"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="18">
+      <c r="D140" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E140" s="9"/>
+      <c r="F140" s="9"/>
+      <c r="G140" s="10"/>
+      <c r="H140" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="13" t="s">
         <v>291</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C141" s="12">
+      <c r="C141" s="11">
         <v>59</v>
       </c>
-      <c r="D141" s="9"/>
-      <c r="E141" s="10"/>
-      <c r="F141" s="10"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="18">
+      <c r="D141" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="10"/>
+      <c r="H141" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="13" t="s">
         <v>263</v>
       </c>
       <c r="B142" s="7" t="s">
@@ -3930,16 +4264,18 @@
       <c r="C142" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D142" s="9"/>
-      <c r="E142" s="10"/>
-      <c r="F142" s="10"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="18">
+      <c r="D142" s="19">
+        <v>73</v>
+      </c>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="10"/>
+      <c r="H142" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="14" t="s">
+      <c r="A143" s="13" t="s">
         <v>265</v>
       </c>
       <c r="B143" s="7" t="s">
@@ -3948,34 +4284,38 @@
       <c r="C143" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D143" s="9"/>
-      <c r="E143" s="10"/>
-      <c r="F143" s="10"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="18">
+      <c r="D143" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="10"/>
+      <c r="H143" s="17">
         <v>18.18</v>
       </c>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="13" t="s">
         <v>268</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="12">
+      <c r="C144" s="11">
         <v>48</v>
       </c>
-      <c r="D144" s="9"/>
-      <c r="E144" s="10"/>
-      <c r="F144" s="10"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="18">
+      <c r="D144" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" s="9"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="10"/>
+      <c r="H144" s="17">
         <v>51.519999999999996</v>
       </c>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="13" t="s">
         <v>271</v>
       </c>
       <c r="B145" s="7" t="s">
@@ -3984,11 +4324,13 @@
       <c r="C145" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D145" s="17"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="17"/>
-      <c r="G145" s="17"/>
-      <c r="H145" s="18">
+      <c r="D145" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="16"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
+      <c r="H145" s="17">
         <v>0</v>
       </c>
     </row>

--- a/MC9510_E22.xlsx
+++ b/MC9510_E22.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramakrishnan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B409D0-F763-45C1-BA17-310C41E9A481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6A274C-C011-4E3A-AFD3-B110BAC22860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="296">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Assign_3</t>
-  </si>
-  <si>
-    <t>Assign_4</t>
   </si>
   <si>
     <t>Mid_exam</t>
@@ -1423,16 +1420,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:G145"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="6" width="11.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1448,62 +1445,61 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="17">
+        <v>12.120000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="17">
-        <v>12.120000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="C4" s="11">
         <v>87</v>
@@ -1511,79 +1507,83 @@
       <c r="D4" s="19">
         <v>86</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="17">
+      <c r="E4" s="9">
+        <v>86</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17">
+      <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="7" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="17">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="17">
-        <v>18.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="C8" s="11">
         <v>99</v>
@@ -1591,19 +1591,20 @@
       <c r="D8" s="19">
         <v>80</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17">
+      <c r="E8" s="9">
+        <v>99</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="11">
         <v>99</v>
@@ -1611,19 +1612,20 @@
       <c r="D9" s="19">
         <v>77</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="17">
+      <c r="E9" s="9">
+        <v>70</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="C10" s="11">
         <v>60</v>
@@ -1631,39 +1633,41 @@
       <c r="D10" s="19">
         <v>55</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17">
+      <c r="E10" s="9">
+        <v>75</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="17">
         <v>72.72999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="C12" s="11">
         <v>88</v>
@@ -1671,19 +1675,20 @@
       <c r="D12" s="19">
         <v>75.5</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="17">
+      <c r="E12" s="9">
+        <v>74</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="C13" s="11">
         <v>90</v>
@@ -1691,19 +1696,20 @@
       <c r="D13" s="19">
         <v>69</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="17">
+      <c r="E13" s="9">
+        <v>66</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="17">
         <v>96.97</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C14" s="11">
         <v>70</v>
@@ -1711,99 +1717,104 @@
       <c r="D14" s="20">
         <v>78</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17">
+      <c r="E14" s="9">
+        <v>90</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="17">
+      <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="7" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="17">
+      <c r="B17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="7" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="C18" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="C19" s="11">
         <v>72</v>
@@ -1811,19 +1822,20 @@
       <c r="D19" s="19">
         <v>48</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="17">
+      <c r="E19" s="9">
+        <v>56</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="C20" s="11">
         <v>96</v>
@@ -1831,19 +1843,20 @@
       <c r="D20" s="19">
         <v>87</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="17">
+      <c r="E20" s="9">
+        <v>68</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="C21" s="11">
         <v>88</v>
@@ -1851,39 +1864,41 @@
       <c r="D21" s="19">
         <v>51</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="17">
+      <c r="E21" s="9">
+        <v>62</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="C23" s="11">
         <v>97</v>
@@ -1891,19 +1906,20 @@
       <c r="D23" s="19">
         <v>91</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="17">
+      <c r="E23" s="9">
+        <v>81</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="17">
         <v>93.94</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7">
       <c r="A24" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="C24" s="11">
         <v>99</v>
@@ -1911,19 +1927,20 @@
       <c r="D24" s="19">
         <v>92</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="17">
+      <c r="E24" s="9">
+        <v>94</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="C25" s="11">
         <v>58</v>
@@ -1931,39 +1948,41 @@
       <c r="D25" s="19">
         <v>74</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="17">
+      <c r="E25" s="9">
+        <v>76</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:7">
       <c r="A26" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="17">
+        <v>12.120000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="17">
-        <v>12.120000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="C27" s="11">
         <v>96</v>
@@ -1971,19 +1990,20 @@
       <c r="D27" s="19">
         <v>82</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="17">
+      <c r="E27" s="9">
+        <v>80</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:7">
       <c r="A28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="C28" s="11">
         <v>77</v>
@@ -1991,19 +2011,20 @@
       <c r="D28" s="19">
         <v>66</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="17">
+      <c r="E28" s="9">
+        <v>94</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="14" t="s">
         <v>63</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>64</v>
       </c>
       <c r="C29" s="11">
         <v>100</v>
@@ -2011,19 +2032,20 @@
       <c r="D29" s="19">
         <v>73.5</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="17">
+      <c r="E29" s="9">
+        <v>76</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="C30" s="11">
         <v>99</v>
@@ -2031,19 +2053,20 @@
       <c r="D30" s="19">
         <v>82</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="17">
+      <c r="E30" s="9">
+        <v>58</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="17">
         <v>93.94</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="C31" s="11">
         <v>100</v>
@@ -2051,39 +2074,41 @@
       <c r="D31" s="19">
         <v>80</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="17">
+      <c r="E31" s="9">
+        <v>69</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="C32" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="C33" s="11">
         <v>74</v>
@@ -2091,19 +2116,20 @@
       <c r="D33" s="19">
         <v>71</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="17">
+      <c r="E33" s="9">
+        <v>49</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="C34" s="11">
         <v>98</v>
@@ -2111,79 +2137,83 @@
       <c r="D34" s="19">
         <v>73</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="17">
+      <c r="E34" s="9">
+        <v>69</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="17">
+      <c r="B36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="7" t="s">
+    <row r="37" spans="1:7">
+      <c r="A37" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="17">
+      <c r="B37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="7" t="s">
+    <row r="38" spans="1:7">
+      <c r="A38" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="C38" s="11">
         <v>61</v>
@@ -2191,19 +2221,20 @@
       <c r="D38" s="19">
         <v>78</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="17">
+      <c r="E38" s="9">
+        <v>74</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:7">
       <c r="A39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="C39" s="11">
         <v>82</v>
@@ -2211,19 +2242,20 @@
       <c r="D39" s="19">
         <v>67</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="17">
+      <c r="E39" s="9">
+        <v>90</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="C40" s="11">
         <v>65</v>
@@ -2231,19 +2263,20 @@
       <c r="D40" s="19">
         <v>43</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="17">
+      <c r="E40" s="9">
+        <v>53</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7">
       <c r="A41" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="C41" s="11">
         <v>70</v>
@@ -2251,59 +2284,62 @@
       <c r="D41" s="19">
         <v>60</v>
       </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="17">
+      <c r="E41" s="9">
+        <v>68</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:7">
       <c r="A42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="C42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="17">
+      <c r="B43" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="10"/>
+      <c r="G43" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="7" t="s">
+    <row r="44" spans="1:7">
+      <c r="A44" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="12" t="s">
+      <c r="B44" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="C44" s="11">
         <v>79</v>
@@ -2311,19 +2347,20 @@
       <c r="D44" s="19">
         <v>76</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="17">
+      <c r="E44" s="9">
+        <v>70</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="C45" s="11">
         <v>96</v>
@@ -2331,19 +2368,20 @@
       <c r="D45" s="19">
         <v>73</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="17">
+      <c r="E45" s="9">
+        <v>71</v>
+      </c>
+      <c r="F45" s="10"/>
+      <c r="G45" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:7">
       <c r="A46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="C46" s="11">
         <v>96</v>
@@ -2351,19 +2389,20 @@
       <c r="D46" s="19">
         <v>85</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="17">
+      <c r="E46" s="9">
+        <v>55</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:7">
       <c r="A47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="C47" s="11">
         <v>96</v>
@@ -2371,19 +2410,20 @@
       <c r="D47" s="19">
         <v>87</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="17">
+      <c r="E47" s="9">
+        <v>86</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="17">
         <v>96.97</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:7">
       <c r="A48" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="C48" s="11">
         <v>99</v>
@@ -2391,19 +2431,20 @@
       <c r="D48" s="19">
         <v>63</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="17">
+      <c r="E48" s="9">
+        <v>86</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:7">
       <c r="A49" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="C49" s="11">
         <v>98</v>
@@ -2411,19 +2452,20 @@
       <c r="D49" s="19">
         <v>80</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="17">
+      <c r="E49" s="9">
+        <v>90</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:7">
       <c r="A50" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="C50" s="11">
         <v>98</v>
@@ -2431,39 +2473,41 @@
       <c r="D50" s="19">
         <v>79</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="17">
+      <c r="E50" s="9">
+        <v>90</v>
+      </c>
+      <c r="F50" s="10"/>
+      <c r="G50" s="17">
         <v>66.67</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:7">
       <c r="A51" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="C51" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="10"/>
+      <c r="G51" s="17">
+        <v>6.0600000000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="17">
-        <v>6.0600000000000005</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="C52" s="11">
         <v>96</v>
@@ -2471,19 +2515,20 @@
       <c r="D52" s="19">
         <v>86</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="17">
+      <c r="E52" s="9">
+        <v>76</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="17">
         <v>66.67</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:7">
       <c r="A53" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="C53" s="11">
         <v>65</v>
@@ -2491,19 +2536,20 @@
       <c r="D53" s="19">
         <v>84</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="17">
+      <c r="E53" s="9">
+        <v>73</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="17">
         <v>63.639999999999993</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:7">
       <c r="A54" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="C54" s="11">
         <v>91</v>
@@ -2511,19 +2557,20 @@
       <c r="D54" s="21">
         <v>74</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="17">
+      <c r="E54" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="17">
         <v>96.97</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:7">
       <c r="A55" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="C55" s="11">
         <v>95</v>
@@ -2531,59 +2578,62 @@
       <c r="D55" s="19">
         <v>94.5</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="17">
+      <c r="E55" s="9">
+        <v>79</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:7">
       <c r="A56" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="10"/>
+      <c r="G56" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="C57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="10"/>
+      <c r="G57" s="17">
+        <v>6.0600000000000005</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="17">
-        <v>6.0600000000000005</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="13" t="s">
+      <c r="B58" s="14" t="s">
         <v>121</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>122</v>
       </c>
       <c r="C58" s="11">
         <v>80</v>
@@ -2591,19 +2641,20 @@
       <c r="D58" s="19">
         <v>84</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="17">
+      <c r="E58" s="9">
+        <v>83</v>
+      </c>
+      <c r="F58" s="10"/>
+      <c r="G58" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:7">
       <c r="A59" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="C59" s="11">
         <v>93</v>
@@ -2611,19 +2662,20 @@
       <c r="D59" s="19">
         <v>80</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="17">
+      <c r="E59" s="9">
+        <v>99</v>
+      </c>
+      <c r="F59" s="10"/>
+      <c r="G59" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:7">
       <c r="A60" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="C60" s="11">
         <v>75</v>
@@ -2631,39 +2683,41 @@
       <c r="D60" s="19">
         <v>79</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="17">
+      <c r="E60" s="9">
+        <v>55</v>
+      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:7">
       <c r="A61" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="C61" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="10"/>
+      <c r="G61" s="17">
+        <v>6.0600000000000005</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="17">
-        <v>6.0600000000000005</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="C62" s="11">
         <v>76</v>
@@ -2671,39 +2725,41 @@
       <c r="D62" s="19">
         <v>66.5</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="17">
+      <c r="E62" s="9">
+        <v>69</v>
+      </c>
+      <c r="F62" s="10"/>
+      <c r="G62" s="17">
         <v>69.699999999999989</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:7">
       <c r="A63" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B63" s="14" t="s">
-        <v>132</v>
-      </c>
       <c r="C63" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" s="19">
         <v>40</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="17">
+      <c r="E63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="10"/>
+      <c r="G63" s="17">
         <v>6.0600000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:7">
       <c r="A64" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>134</v>
       </c>
       <c r="C64" s="11">
         <v>85</v>
@@ -2711,59 +2767,62 @@
       <c r="D64" s="19">
         <v>55</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="17">
+      <c r="E64" s="9">
+        <v>71</v>
+      </c>
+      <c r="F64" s="10"/>
+      <c r="G64" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:7">
       <c r="A65" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="C65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="10"/>
+      <c r="G65" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="C66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="10"/>
+      <c r="G66" s="17">
+        <v>6.0600000000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="17">
-        <v>6.0600000000000005</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="13" t="s">
+      <c r="B67" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="C67" s="11">
         <v>81</v>
@@ -2771,39 +2830,41 @@
       <c r="D67" s="19">
         <v>74</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="17">
+      <c r="E67" s="9">
+        <v>73</v>
+      </c>
+      <c r="F67" s="10"/>
+      <c r="G67" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:7">
       <c r="A68" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="C68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="10"/>
+      <c r="G68" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="C69" s="11">
         <v>94</v>
@@ -2811,39 +2872,41 @@
       <c r="D69" s="19">
         <v>85</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="17">
+      <c r="E69" s="9">
+        <v>90</v>
+      </c>
+      <c r="F69" s="10"/>
+      <c r="G69" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:7">
       <c r="A70" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="C70" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="10"/>
+      <c r="G70" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="C71" s="11">
         <v>78</v>
@@ -2851,19 +2914,20 @@
       <c r="D71" s="19">
         <v>64</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="17">
+      <c r="E71" s="9">
+        <v>88</v>
+      </c>
+      <c r="F71" s="10"/>
+      <c r="G71" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:7">
       <c r="A72" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="C72" s="11">
         <v>95</v>
@@ -2871,19 +2935,20 @@
       <c r="D72" s="19">
         <v>86</v>
       </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="17">
+      <c r="E72" s="9">
+        <v>19</v>
+      </c>
+      <c r="F72" s="10"/>
+      <c r="G72" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:7">
       <c r="A73" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="C73" s="11">
         <v>93</v>
@@ -2891,19 +2956,20 @@
       <c r="D73" s="19">
         <v>79.5</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="17">
+      <c r="E73" s="9">
+        <v>59</v>
+      </c>
+      <c r="F73" s="10"/>
+      <c r="G73" s="17">
         <v>72.72999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:7">
       <c r="A74" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="C74" s="11">
         <v>96</v>
@@ -2911,19 +2977,20 @@
       <c r="D74" s="19">
         <v>95</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="17">
+      <c r="E74" s="9">
+        <v>90</v>
+      </c>
+      <c r="F74" s="10"/>
+      <c r="G74" s="17">
         <v>93.94</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:7">
       <c r="A75" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>156</v>
       </c>
       <c r="C75" s="11">
         <v>98</v>
@@ -2931,19 +2998,20 @@
       <c r="D75" s="19">
         <v>94</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="17">
+      <c r="E75" s="9">
+        <v>99</v>
+      </c>
+      <c r="F75" s="10"/>
+      <c r="G75" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:7">
       <c r="A76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="C76" s="11">
         <v>100</v>
@@ -2951,19 +3019,20 @@
       <c r="D76" s="19">
         <v>83</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="17">
+      <c r="E76" s="9">
+        <v>75</v>
+      </c>
+      <c r="F76" s="10"/>
+      <c r="G76" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:7">
       <c r="A77" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="C77" s="11">
         <v>98</v>
@@ -2971,39 +3040,41 @@
       <c r="D77" s="19">
         <v>70</v>
       </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="17">
+      <c r="E77" s="9">
+        <v>97</v>
+      </c>
+      <c r="F77" s="10"/>
+      <c r="G77" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:7">
       <c r="A78" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="C78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="10"/>
+      <c r="G78" s="17">
+        <v>6.0600000000000005</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="17">
-        <v>6.0600000000000005</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="6" t="s">
+      <c r="B79" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>164</v>
       </c>
       <c r="C79" s="11">
         <v>72</v>
@@ -3011,59 +3082,62 @@
       <c r="D79" s="19">
         <v>84</v>
       </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="17">
+      <c r="E79" s="9">
+        <v>74</v>
+      </c>
+      <c r="F79" s="10"/>
+      <c r="G79" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:7">
       <c r="A80" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="C80" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="10"/>
+      <c r="G80" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="6" t="s">
+      <c r="B81" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="C81" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="10"/>
+      <c r="G81" s="17">
+        <v>3.0300000000000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="17">
-        <v>3.0300000000000002</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="6" t="s">
+      <c r="B82" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>170</v>
       </c>
       <c r="C82" s="11">
         <v>74</v>
@@ -3071,39 +3145,41 @@
       <c r="D82" s="19">
         <v>79</v>
       </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="17">
+      <c r="E82" s="9">
+        <v>80</v>
+      </c>
+      <c r="F82" s="10"/>
+      <c r="G82" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:7">
       <c r="A83" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="C83" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="10"/>
+      <c r="G83" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="6" t="s">
+      <c r="B84" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>174</v>
       </c>
       <c r="C84" s="11">
         <v>43</v>
@@ -3111,39 +3187,41 @@
       <c r="D84" s="19">
         <v>69</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="17">
+      <c r="E84" s="9">
+        <v>84</v>
+      </c>
+      <c r="F84" s="10"/>
+      <c r="G84" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:7">
       <c r="A85" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="C85" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="10"/>
+      <c r="G85" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="6" t="s">
+      <c r="B86" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="C86" s="11">
         <v>99</v>
@@ -3151,19 +3229,20 @@
       <c r="D86" s="19">
         <v>81</v>
       </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="17">
+      <c r="E86" s="9">
+        <v>59</v>
+      </c>
+      <c r="F86" s="10"/>
+      <c r="G86" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:7">
       <c r="A87" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="C87" s="11">
         <v>99</v>
@@ -3171,19 +3250,20 @@
       <c r="D87" s="19">
         <v>83</v>
       </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="17">
+      <c r="E87" s="9">
+        <v>69</v>
+      </c>
+      <c r="F87" s="10"/>
+      <c r="G87" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:7">
       <c r="A88" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="C88" s="11">
         <v>85</v>
@@ -3191,59 +3271,62 @@
       <c r="D88" s="19">
         <v>56</v>
       </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="17">
+      <c r="E88" s="9">
+        <v>55</v>
+      </c>
+      <c r="F88" s="10"/>
+      <c r="G88" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:7">
       <c r="A89" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="C89" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="10"/>
+      <c r="G89" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="17">
+      <c r="B90" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="10"/>
+      <c r="G90" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B90" s="7" t="s">
+    <row r="91" spans="1:7">
+      <c r="A91" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="6" t="s">
+      <c r="B91" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>188</v>
       </c>
       <c r="C91" s="11">
         <v>93</v>
@@ -3251,39 +3334,41 @@
       <c r="D91" s="19">
         <v>67</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="17">
+      <c r="E91" s="9">
+        <v>91</v>
+      </c>
+      <c r="F91" s="10"/>
+      <c r="G91" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:7">
       <c r="A92" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B92" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="C92" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="10"/>
+      <c r="G92" s="17">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="17">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="6" t="s">
+      <c r="B93" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="C93" s="11">
         <v>99</v>
@@ -3291,19 +3376,20 @@
       <c r="D93" s="19">
         <v>84</v>
       </c>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="17">
+      <c r="E93" s="9">
+        <v>68</v>
+      </c>
+      <c r="F93" s="10"/>
+      <c r="G93" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:7">
       <c r="A94" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>194</v>
       </c>
       <c r="C94" s="11">
         <v>70</v>
@@ -3311,19 +3397,20 @@
       <c r="D94" s="19">
         <v>90</v>
       </c>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="17">
+      <c r="E94" s="9">
+        <v>86</v>
+      </c>
+      <c r="F94" s="10"/>
+      <c r="G94" s="17">
         <v>96.97</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7">
       <c r="A95" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B95" s="7" t="s">
         <v>195</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="C95" s="11">
         <v>90</v>
@@ -3331,19 +3418,20 @@
       <c r="D95" s="19">
         <v>79</v>
       </c>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="17">
+      <c r="E95" s="9">
+        <v>72</v>
+      </c>
+      <c r="F95" s="10"/>
+      <c r="G95" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:7">
       <c r="A96" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="C96" s="11">
         <v>82</v>
@@ -3351,37 +3439,39 @@
       <c r="D96" s="19">
         <v>59.5</v>
       </c>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="17">
+      <c r="E96" s="9">
+        <v>64</v>
+      </c>
+      <c r="F96" s="10"/>
+      <c r="G96" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:7">
       <c r="A97" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="C97" s="11">
         <v>55</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="17"/>
-    </row>
-    <row r="98" spans="1:8">
+        <v>9</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="10"/>
+      <c r="G97" s="17"/>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>202</v>
       </c>
       <c r="C98" s="11">
         <v>100</v>
@@ -3389,39 +3479,41 @@
       <c r="D98" s="19">
         <v>89</v>
       </c>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="17">
+      <c r="E98" s="9">
+        <v>88</v>
+      </c>
+      <c r="F98" s="10"/>
+      <c r="G98" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:7">
       <c r="A99" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="C99" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="10"/>
+      <c r="G99" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="6" t="s">
+      <c r="B100" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>206</v>
       </c>
       <c r="C100" s="11">
         <v>93</v>
@@ -3429,19 +3521,20 @@
       <c r="D100" s="19">
         <v>86</v>
       </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="17">
+      <c r="E100" s="9">
+        <v>73</v>
+      </c>
+      <c r="F100" s="10"/>
+      <c r="G100" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:7">
       <c r="A101" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="C101" s="11">
         <v>81</v>
@@ -3449,19 +3542,20 @@
       <c r="D101" s="19">
         <v>71</v>
       </c>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="17">
+      <c r="E101" s="9">
+        <v>55</v>
+      </c>
+      <c r="F101" s="10"/>
+      <c r="G101" s="17">
         <v>83.33</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:7">
       <c r="A102" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B102" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>210</v>
       </c>
       <c r="C102" s="11">
         <v>71</v>
@@ -3469,39 +3563,41 @@
       <c r="D102" s="19">
         <v>55</v>
       </c>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="17">
+      <c r="E102" s="9">
+        <v>67</v>
+      </c>
+      <c r="F102" s="10"/>
+      <c r="G102" s="17">
         <v>81.820000000000007</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:7">
       <c r="A103" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B103" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="C103" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="10"/>
+      <c r="G103" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="6" t="s">
+      <c r="B104" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="C104" s="11">
         <v>85</v>
@@ -3509,39 +3605,41 @@
       <c r="D104" s="19">
         <v>88</v>
       </c>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="17">
+      <c r="E104" s="9">
+        <v>47</v>
+      </c>
+      <c r="F104" s="10"/>
+      <c r="G104" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:7">
       <c r="A105" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="C105" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="10"/>
+      <c r="G105" s="17">
+        <v>3.0300000000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="9"/>
-      <c r="F105" s="9"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="17">
-        <v>3.0300000000000002</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="6" t="s">
+      <c r="B106" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="C106" s="11">
         <v>71</v>
@@ -3549,19 +3647,20 @@
       <c r="D106" s="19">
         <v>65</v>
       </c>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="17">
+      <c r="E106" s="9">
+        <v>57</v>
+      </c>
+      <c r="F106" s="10"/>
+      <c r="G106" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:7">
       <c r="A107" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B107" s="14" t="s">
         <v>219</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>220</v>
       </c>
       <c r="C107" s="11">
         <v>98</v>
@@ -3569,19 +3668,20 @@
       <c r="D107" s="19">
         <v>55</v>
       </c>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="17">
+      <c r="E107" s="9">
+        <v>85</v>
+      </c>
+      <c r="F107" s="10"/>
+      <c r="G107" s="17">
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:7">
       <c r="A108" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B108" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>222</v>
       </c>
       <c r="C108" s="11">
         <v>83</v>
@@ -3589,19 +3689,20 @@
       <c r="D108" s="19">
         <v>91</v>
       </c>
-      <c r="E108" s="9"/>
-      <c r="F108" s="9"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="17">
+      <c r="E108" s="9">
+        <v>84</v>
+      </c>
+      <c r="F108" s="10"/>
+      <c r="G108" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7">
       <c r="A109" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="C109" s="11">
         <v>73</v>
@@ -3609,39 +3710,41 @@
       <c r="D109" s="19">
         <v>65</v>
       </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="17">
+      <c r="E109" s="9">
+        <v>63</v>
+      </c>
+      <c r="F109" s="10"/>
+      <c r="G109" s="17">
         <v>87.88</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:7">
       <c r="A110" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B110" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="C110" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="10"/>
+      <c r="G110" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D110" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="6" t="s">
+      <c r="B111" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="C111" s="11">
         <v>99</v>
@@ -3649,39 +3752,41 @@
       <c r="D111" s="19">
         <v>81</v>
       </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="17">
+      <c r="E111" s="9">
+        <v>68</v>
+      </c>
+      <c r="F111" s="10"/>
+      <c r="G111" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:7">
       <c r="A112" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="C112" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="10"/>
+      <c r="G112" s="17">
+        <v>3.0300000000000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="17">
-        <v>3.0300000000000002</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="13" t="s">
+      <c r="B113" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="C113" s="11">
         <v>89</v>
@@ -3689,317 +3794,333 @@
       <c r="D113" s="19">
         <v>87</v>
       </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="17">
+      <c r="E113" s="9">
+        <v>85</v>
+      </c>
+      <c r="F113" s="10"/>
+      <c r="G113" s="17">
         <v>90.91</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:7">
       <c r="A114" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B114" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C114" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="17">
+        <v>9</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="10"/>
+      <c r="G114" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:7">
       <c r="A115" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B115" s="7" t="s">
         <v>236</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>237</v>
       </c>
       <c r="C115" s="11">
         <v>64</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="9"/>
-      <c r="F115" s="9"/>
-      <c r="G115" s="10"/>
-      <c r="H115" s="17"/>
-    </row>
-    <row r="116" spans="1:8">
+        <v>9</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="10"/>
+      <c r="G115" s="17"/>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="10"/>
-      <c r="H116" s="17">
+        <v>9</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="10"/>
+      <c r="G116" s="17">
         <v>12.120000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:7">
       <c r="A117" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B117" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="C117" s="11">
         <v>61</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="10"/>
-      <c r="H117" s="17">
+        <v>9</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="10"/>
+      <c r="G117" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:7">
       <c r="A118" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B118" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="C118" s="11">
         <v>75</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="17">
+        <v>9</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="10"/>
+      <c r="G118" s="17">
         <v>30.3</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:7">
       <c r="A119" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="C119" s="11">
         <v>49</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="10"/>
-      <c r="H119" s="17">
+        <v>9</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="10"/>
+      <c r="G119" s="17">
         <v>15.15</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:7">
       <c r="A120" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="C120" s="11">
         <v>59</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="10"/>
-      <c r="H120" s="17">
+        <v>9</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="10"/>
+      <c r="G120" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:7">
       <c r="A121" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>254</v>
       </c>
       <c r="C121" s="11">
         <v>47</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="10"/>
-      <c r="H121" s="17">
+        <v>9</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="10"/>
+      <c r="G121" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:7">
       <c r="A122" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B122" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>257</v>
       </c>
       <c r="C122" s="11">
         <v>61</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="10"/>
-      <c r="H122" s="17">
+        <v>9</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="10"/>
+      <c r="G122" s="17">
         <v>9.09</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:7">
       <c r="A123" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="10"/>
-      <c r="H123" s="17">
+        <v>9</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="10"/>
+      <c r="G123" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:7">
       <c r="A124" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B124" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>262</v>
       </c>
       <c r="C124" s="11">
         <v>75</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="10"/>
-      <c r="H124" s="17">
+        <v>9</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="10"/>
+      <c r="G124" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:7">
       <c r="A125" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="10"/>
-      <c r="H125" s="17">
+        <v>9</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="10"/>
+      <c r="G125" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:7">
       <c r="A126" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B126" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="C126" s="11">
         <v>37</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="10"/>
-      <c r="H126" s="17">
+        <v>9</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="10"/>
+      <c r="G126" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:7">
       <c r="A127" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B127" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>270</v>
       </c>
       <c r="C127" s="11">
         <v>79</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="10"/>
-      <c r="H127" s="17">
+        <v>9</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="10"/>
+      <c r="G127" s="17">
         <v>15.15</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:7">
       <c r="A128" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>273</v>
       </c>
       <c r="C128" s="11">
         <v>62</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="10"/>
-      <c r="H128" s="17">
+        <v>9</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="10"/>
+      <c r="G128" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:7">
       <c r="A129" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C129" s="11">
         <v>67</v>
@@ -4007,59 +4128,62 @@
       <c r="D129" s="19">
         <v>59</v>
       </c>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="10"/>
-      <c r="H129" s="17">
+      <c r="E129" s="9">
+        <v>62</v>
+      </c>
+      <c r="F129" s="10"/>
+      <c r="G129" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:7">
       <c r="A130" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B130" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="C130" s="11">
         <v>99</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="10"/>
-      <c r="H130" s="17">
+        <v>9</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="10"/>
+      <c r="G130" s="17">
         <v>21.21</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:7">
       <c r="A131" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B131" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="C131" s="11">
         <v>85</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="10"/>
-      <c r="H131" s="17">
+        <v>9</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="10"/>
+      <c r="G131" s="17">
         <v>9.09</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:7">
       <c r="A132" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C132" s="11">
         <v>48</v>
@@ -4067,39 +4191,41 @@
       <c r="D132" s="19">
         <v>31</v>
       </c>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="10"/>
-      <c r="H132" s="17">
+      <c r="E132" s="9">
+        <v>38</v>
+      </c>
+      <c r="F132" s="10"/>
+      <c r="G132" s="17">
         <v>75.760000000000005</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:7">
       <c r="A133" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B133" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="C133" s="11">
         <v>55</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="17">
+        <v>9</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="10"/>
+      <c r="G133" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:7">
       <c r="A134" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C134" s="11">
         <v>72</v>
@@ -4107,230 +4233,242 @@
       <c r="D134" s="19">
         <v>54</v>
       </c>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="10"/>
-      <c r="H134" s="17">
+      <c r="E134" s="9">
+        <v>47</v>
+      </c>
+      <c r="F134" s="10"/>
+      <c r="G134" s="17">
         <v>84.850000000000009</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:7">
       <c r="A135" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>284</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>285</v>
       </c>
       <c r="C135" s="11">
         <v>77</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="10"/>
-      <c r="H135" s="17">
+        <v>9</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="10"/>
+      <c r="G135" s="17">
         <v>15.15</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:7">
       <c r="A136" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B136" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="10"/>
+      <c r="G136" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B137" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C136" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="10"/>
-      <c r="H136" s="17">
+      <c r="C137" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="10"/>
+      <c r="G137" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="B137" s="7" t="s">
+    <row r="138" spans="1:7">
+      <c r="A138" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C137" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="10"/>
-      <c r="H137" s="17">
+      <c r="C138" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" s="10"/>
+      <c r="G138" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="B138" s="7" t="s">
+    <row r="139" spans="1:7">
+      <c r="A139" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B139" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C138" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="10"/>
-      <c r="H138" s="17">
+      <c r="C139" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="10"/>
+      <c r="G139" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="B139" s="7" t="s">
+    <row r="140" spans="1:7">
+      <c r="A140" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B140" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C139" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D139" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="10"/>
-      <c r="H139" s="17">
+      <c r="C140" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="10"/>
+      <c r="G140" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B140" s="7" t="s">
+    <row r="141" spans="1:7">
+      <c r="A141" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C140" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D140" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="10"/>
-      <c r="H140" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="13" t="s">
+      <c r="B141" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="C141" s="11">
         <v>59</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="10"/>
-      <c r="H141" s="17">
+        <v>9</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="10"/>
+      <c r="G141" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:7">
       <c r="A142" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D142" s="19">
         <v>73</v>
       </c>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="10"/>
-      <c r="H142" s="17">
+      <c r="E142" s="9">
+        <v>98</v>
+      </c>
+      <c r="F142" s="10"/>
+      <c r="G142" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:7">
       <c r="A143" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="10"/>
+      <c r="G143" s="17">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="10"/>
-      <c r="H143" s="17">
-        <v>18.18</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>295</v>
       </c>
       <c r="C144" s="11">
         <v>48</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="10"/>
-      <c r="H144" s="17">
+        <v>9</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="10"/>
+      <c r="G144" s="17">
         <v>51.519999999999996</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:7">
       <c r="A145" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E145" s="16"/>
+        <v>9</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="F145" s="16"/>
-      <c r="G145" s="16"/>
-      <c r="H145" s="17">
+      <c r="G145" s="17">
         <v>0</v>
       </c>
     </row>

--- a/MC9510_E22.xlsx
+++ b/MC9510_E22.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramakrishnan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pafiya.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6A274C-C011-4E3A-AFD3-B110BAC22860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="296">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -924,7 +923,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -1127,7 +1126,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1143,11 +1141,14 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1419,14 +1420,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="31.1796875" customWidth="1"/>
-    <col min="3" max="6" width="11.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1462,14 +1463,16 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="17">
+      <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1483,14 +1486,16 @@
       <c r="C3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="17">
+      <c r="F3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="16">
         <v>12.120000000000001</v>
       </c>
     </row>
@@ -1504,14 +1509,16 @@
       <c r="C4" s="11">
         <v>87</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="18">
         <v>86</v>
       </c>
       <c r="E4" s="9">
         <v>86</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="17">
+      <c r="F4" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="G4" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -1525,14 +1532,16 @@
       <c r="C5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="17">
+      <c r="F5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1546,14 +1555,16 @@
       <c r="C6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="17">
+      <c r="F6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1567,14 +1578,16 @@
       <c r="C7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="17">
+      <c r="F7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="16">
         <v>18.18</v>
       </c>
     </row>
@@ -1588,14 +1601,16 @@
       <c r="C8" s="11">
         <v>99</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <v>80</v>
       </c>
       <c r="E8" s="9">
         <v>99</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="17">
+      <c r="F8" s="10">
+        <v>89</v>
+      </c>
+      <c r="G8" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -1609,14 +1624,16 @@
       <c r="C9" s="11">
         <v>99</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="18">
         <v>77</v>
       </c>
       <c r="E9" s="9">
         <v>70</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="17">
+      <c r="F9" s="10">
+        <v>84</v>
+      </c>
+      <c r="G9" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -1630,14 +1647,16 @@
       <c r="C10" s="11">
         <v>60</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="18">
         <v>55</v>
       </c>
       <c r="E10" s="9">
         <v>75</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="17">
+      <c r="F10" s="10">
+        <v>96</v>
+      </c>
+      <c r="G10" s="16">
         <v>72.72999999999999</v>
       </c>
     </row>
@@ -1651,14 +1670,16 @@
       <c r="C11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="17">
+      <c r="F11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -1672,14 +1693,16 @@
       <c r="C12" s="11">
         <v>88</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <v>75.5</v>
       </c>
       <c r="E12" s="9">
         <v>74</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="17">
+      <c r="F12" s="10">
+        <v>74</v>
+      </c>
+      <c r="G12" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1693,14 +1716,16 @@
       <c r="C13" s="11">
         <v>90</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <v>69</v>
       </c>
       <c r="E13" s="9">
         <v>66</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="17">
+      <c r="F13" s="10">
+        <v>69</v>
+      </c>
+      <c r="G13" s="16">
         <v>96.97</v>
       </c>
     </row>
@@ -1714,14 +1739,16 @@
       <c r="C14" s="11">
         <v>70</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>78</v>
       </c>
       <c r="E14" s="9">
         <v>90</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="17">
+      <c r="F14" s="10">
+        <v>97</v>
+      </c>
+      <c r="G14" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -1735,14 +1762,16 @@
       <c r="C15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="17">
+      <c r="F15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1756,14 +1785,16 @@
       <c r="C16" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="17">
+      <c r="F16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1777,14 +1808,16 @@
       <c r="C17" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="17">
+      <c r="F17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1798,14 +1831,16 @@
       <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="17">
+      <c r="F18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -1819,14 +1854,16 @@
       <c r="C19" s="11">
         <v>72</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="18">
         <v>48</v>
       </c>
       <c r="E19" s="9">
         <v>56</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="17">
+      <c r="F19" s="10">
+        <v>77</v>
+      </c>
+      <c r="G19" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1840,14 +1877,16 @@
       <c r="C20" s="11">
         <v>96</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="18">
         <v>87</v>
       </c>
       <c r="E20" s="9">
         <v>68</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="17">
+      <c r="F20" s="10">
+        <v>72.5</v>
+      </c>
+      <c r="G20" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -1861,14 +1900,16 @@
       <c r="C21" s="11">
         <v>88</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="18">
         <v>51</v>
       </c>
       <c r="E21" s="9">
         <v>62</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="17">
+      <c r="F21" s="10">
+        <v>84.5</v>
+      </c>
+      <c r="G21" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -1882,14 +1923,16 @@
       <c r="C22" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="17">
+      <c r="F22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="16">
         <v>0</v>
       </c>
     </row>
@@ -1903,14 +1946,16 @@
       <c r="C23" s="11">
         <v>97</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="18">
         <v>91</v>
       </c>
       <c r="E23" s="9">
         <v>81</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="17">
+      <c r="F23" s="10">
+        <v>73</v>
+      </c>
+      <c r="G23" s="16">
         <v>93.94</v>
       </c>
     </row>
@@ -1924,14 +1969,16 @@
       <c r="C24" s="11">
         <v>99</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="18">
         <v>92</v>
       </c>
       <c r="E24" s="9">
         <v>94</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="17">
+      <c r="F24" s="21">
+        <v>79</v>
+      </c>
+      <c r="G24" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -1945,14 +1992,16 @@
       <c r="C25" s="11">
         <v>58</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="18">
         <v>74</v>
       </c>
       <c r="E25" s="9">
         <v>76</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="17">
+      <c r="F25" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="G25" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -1966,14 +2015,16 @@
       <c r="C26" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="17">
+      <c r="F26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="16">
         <v>12.120000000000001</v>
       </c>
     </row>
@@ -1987,14 +2038,16 @@
       <c r="C27" s="11">
         <v>96</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="18">
         <v>82</v>
       </c>
       <c r="E27" s="9">
         <v>80</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="17">
+      <c r="F27" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="G27" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2008,14 +2061,16 @@
       <c r="C28" s="11">
         <v>77</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="18">
         <v>66</v>
       </c>
       <c r="E28" s="9">
         <v>94</v>
       </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="17">
+      <c r="F28" s="10">
+        <v>63.75</v>
+      </c>
+      <c r="G28" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -2029,14 +2084,16 @@
       <c r="C29" s="11">
         <v>100</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="18">
         <v>73.5</v>
       </c>
       <c r="E29" s="9">
         <v>76</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="17">
+      <c r="F29" s="10">
+        <v>73</v>
+      </c>
+      <c r="G29" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2050,14 +2107,16 @@
       <c r="C30" s="11">
         <v>99</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="18">
         <v>82</v>
       </c>
       <c r="E30" s="9">
         <v>58</v>
       </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="17">
+      <c r="F30" s="10">
+        <v>76.5</v>
+      </c>
+      <c r="G30" s="16">
         <v>93.94</v>
       </c>
     </row>
@@ -2071,14 +2130,16 @@
       <c r="C31" s="11">
         <v>100</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="18">
         <v>80</v>
       </c>
       <c r="E31" s="9">
         <v>69</v>
       </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="17">
+      <c r="F31" s="10">
+        <v>70</v>
+      </c>
+      <c r="G31" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2092,14 +2153,16 @@
       <c r="C32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="17">
+      <c r="F32" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2113,14 +2176,16 @@
       <c r="C33" s="11">
         <v>74</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="18">
         <v>71</v>
       </c>
       <c r="E33" s="9">
         <v>49</v>
       </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="17">
+      <c r="F33" s="10">
+        <v>76.75</v>
+      </c>
+      <c r="G33" s="16">
         <v>69.699999999999989</v>
       </c>
     </row>
@@ -2134,14 +2199,16 @@
       <c r="C34" s="11">
         <v>98</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="18">
         <v>73</v>
       </c>
       <c r="E34" s="9">
         <v>69</v>
       </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="17">
+      <c r="F34" s="10">
+        <v>83</v>
+      </c>
+      <c r="G34" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2155,14 +2222,16 @@
       <c r="C35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="17">
+      <c r="F35" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2176,14 +2245,16 @@
       <c r="C36" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="17">
+      <c r="F36" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2197,14 +2268,16 @@
       <c r="C37" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="17">
+      <c r="F37" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2218,14 +2291,16 @@
       <c r="C38" s="11">
         <v>61</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="18">
         <v>78</v>
       </c>
       <c r="E38" s="9">
         <v>74</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="17">
+      <c r="F38" s="10">
+        <v>72.5</v>
+      </c>
+      <c r="G38" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2239,14 +2314,16 @@
       <c r="C39" s="11">
         <v>82</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="18">
         <v>67</v>
       </c>
       <c r="E39" s="9">
         <v>90</v>
       </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="17">
+      <c r="F39" s="10">
+        <v>82.75</v>
+      </c>
+      <c r="G39" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2260,14 +2337,16 @@
       <c r="C40" s="11">
         <v>65</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="18">
         <v>43</v>
       </c>
       <c r="E40" s="9">
         <v>53</v>
       </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="17">
+      <c r="F40" s="10">
+        <v>69</v>
+      </c>
+      <c r="G40" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -2281,14 +2360,16 @@
       <c r="C41" s="11">
         <v>70</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="18">
         <v>60</v>
       </c>
       <c r="E41" s="9">
         <v>68</v>
       </c>
-      <c r="F41" s="10"/>
-      <c r="G41" s="17">
+      <c r="F41" s="10">
+        <v>77.5</v>
+      </c>
+      <c r="G41" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2302,14 +2383,16 @@
       <c r="C42" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="17">
+      <c r="F42" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2323,14 +2406,16 @@
       <c r="C43" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="10"/>
-      <c r="G43" s="17">
+      <c r="F43" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2344,14 +2429,16 @@
       <c r="C44" s="11">
         <v>79</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="18">
         <v>76</v>
       </c>
       <c r="E44" s="9">
         <v>70</v>
       </c>
-      <c r="F44" s="10"/>
-      <c r="G44" s="17">
+      <c r="F44" s="10">
+        <v>65</v>
+      </c>
+      <c r="G44" s="16">
         <v>69.699999999999989</v>
       </c>
     </row>
@@ -2365,14 +2452,16 @@
       <c r="C45" s="11">
         <v>96</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="18">
         <v>73</v>
       </c>
       <c r="E45" s="9">
         <v>71</v>
       </c>
-      <c r="F45" s="10"/>
-      <c r="G45" s="17">
+      <c r="F45" s="10">
+        <v>91</v>
+      </c>
+      <c r="G45" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2386,14 +2475,16 @@
       <c r="C46" s="11">
         <v>96</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="18">
         <v>85</v>
       </c>
       <c r="E46" s="9">
         <v>55</v>
       </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="17">
+      <c r="F46" s="10">
+        <v>66</v>
+      </c>
+      <c r="G46" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -2407,14 +2498,16 @@
       <c r="C47" s="11">
         <v>96</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="18">
         <v>87</v>
       </c>
       <c r="E47" s="9">
         <v>86</v>
       </c>
-      <c r="F47" s="10"/>
-      <c r="G47" s="17">
+      <c r="F47" s="10">
+        <v>77</v>
+      </c>
+      <c r="G47" s="16">
         <v>96.97</v>
       </c>
     </row>
@@ -2428,14 +2521,16 @@
       <c r="C48" s="11">
         <v>99</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="18">
         <v>63</v>
       </c>
       <c r="E48" s="9">
         <v>86</v>
       </c>
-      <c r="F48" s="10"/>
-      <c r="G48" s="17">
+      <c r="F48" s="10">
+        <v>78</v>
+      </c>
+      <c r="G48" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -2449,14 +2544,16 @@
       <c r="C49" s="11">
         <v>98</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="18">
         <v>80</v>
       </c>
       <c r="E49" s="9">
         <v>90</v>
       </c>
-      <c r="F49" s="10"/>
-      <c r="G49" s="17">
+      <c r="F49" s="10">
+        <v>77.5</v>
+      </c>
+      <c r="G49" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2470,14 +2567,16 @@
       <c r="C50" s="11">
         <v>98</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="18">
         <v>79</v>
       </c>
       <c r="E50" s="9">
         <v>90</v>
       </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="17">
+      <c r="F50" s="10">
+        <v>78.25</v>
+      </c>
+      <c r="G50" s="16">
         <v>66.67</v>
       </c>
     </row>
@@ -2491,14 +2590,16 @@
       <c r="C51" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F51" s="10"/>
-      <c r="G51" s="17">
+      <c r="F51" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2512,14 +2613,16 @@
       <c r="C52" s="11">
         <v>96</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="18">
         <v>86</v>
       </c>
       <c r="E52" s="9">
         <v>76</v>
       </c>
-      <c r="F52" s="10"/>
-      <c r="G52" s="17">
+      <c r="F52" s="10">
+        <v>85</v>
+      </c>
+      <c r="G52" s="16">
         <v>66.67</v>
       </c>
     </row>
@@ -2533,14 +2636,16 @@
       <c r="C53" s="11">
         <v>65</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="18">
         <v>84</v>
       </c>
       <c r="E53" s="9">
         <v>73</v>
       </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="17">
+      <c r="F53" s="10">
+        <v>80.75</v>
+      </c>
+      <c r="G53" s="16">
         <v>63.639999999999993</v>
       </c>
     </row>
@@ -2554,14 +2659,16 @@
       <c r="C54" s="11">
         <v>91</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="20">
         <v>74</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="10"/>
-      <c r="G54" s="17">
+      <c r="F54" s="10">
+        <v>67.5</v>
+      </c>
+      <c r="G54" s="16">
         <v>96.97</v>
       </c>
     </row>
@@ -2575,14 +2682,16 @@
       <c r="C55" s="11">
         <v>95</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="18">
         <v>94.5</v>
       </c>
       <c r="E55" s="9">
         <v>79</v>
       </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="17">
+      <c r="F55" s="10">
+        <v>77.5</v>
+      </c>
+      <c r="G55" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2596,14 +2705,16 @@
       <c r="C56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="17">
+      <c r="F56" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -2617,14 +2728,16 @@
       <c r="C57" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F57" s="10"/>
-      <c r="G57" s="17">
+      <c r="F57" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2638,14 +2751,16 @@
       <c r="C58" s="11">
         <v>80</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="18">
         <v>84</v>
       </c>
       <c r="E58" s="9">
         <v>83</v>
       </c>
-      <c r="F58" s="10"/>
-      <c r="G58" s="17">
+      <c r="F58" s="10">
+        <v>74</v>
+      </c>
+      <c r="G58" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -2659,14 +2774,16 @@
       <c r="C59" s="11">
         <v>93</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="18">
         <v>80</v>
       </c>
       <c r="E59" s="9">
         <v>99</v>
       </c>
-      <c r="F59" s="10"/>
-      <c r="G59" s="17">
+      <c r="F59" s="10">
+        <v>80</v>
+      </c>
+      <c r="G59" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2680,14 +2797,16 @@
       <c r="C60" s="11">
         <v>75</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="18">
         <v>79</v>
       </c>
       <c r="E60" s="9">
         <v>55</v>
       </c>
-      <c r="F60" s="10"/>
-      <c r="G60" s="17">
+      <c r="F60" s="10">
+        <v>74</v>
+      </c>
+      <c r="G60" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2701,14 +2820,16 @@
       <c r="C61" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F61" s="10"/>
-      <c r="G61" s="17">
+      <c r="F61" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2722,14 +2843,16 @@
       <c r="C62" s="11">
         <v>76</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="18">
         <v>66.5</v>
       </c>
       <c r="E62" s="9">
         <v>69</v>
       </c>
-      <c r="F62" s="10"/>
-      <c r="G62" s="17">
+      <c r="F62" s="10">
+        <v>66</v>
+      </c>
+      <c r="G62" s="16">
         <v>69.699999999999989</v>
       </c>
     </row>
@@ -2743,14 +2866,16 @@
       <c r="C63" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="18">
         <v>40</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="10"/>
-      <c r="G63" s="17">
+      <c r="F63" s="10">
+        <v>58</v>
+      </c>
+      <c r="G63" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2764,14 +2889,16 @@
       <c r="C64" s="11">
         <v>85</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="18">
         <v>55</v>
       </c>
       <c r="E64" s="9">
         <v>71</v>
       </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="17">
+      <c r="F64" s="10">
+        <v>65.5</v>
+      </c>
+      <c r="G64" s="16">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -2785,14 +2912,16 @@
       <c r="C65" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="17">
+      <c r="F65" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -2806,14 +2935,16 @@
       <c r="C66" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F66" s="10"/>
-      <c r="G66" s="17">
+      <c r="F66" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -2827,14 +2958,16 @@
       <c r="C67" s="11">
         <v>81</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="18">
         <v>74</v>
       </c>
       <c r="E67" s="9">
         <v>73</v>
       </c>
-      <c r="F67" s="10"/>
-      <c r="G67" s="17">
+      <c r="F67" s="10">
+        <v>78.5</v>
+      </c>
+      <c r="G67" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -2848,14 +2981,16 @@
       <c r="C68" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F68" s="10"/>
-      <c r="G68" s="17">
+      <c r="F68" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -2869,14 +3004,16 @@
       <c r="C69" s="11">
         <v>94</v>
       </c>
-      <c r="D69" s="19">
+      <c r="D69" s="18">
         <v>85</v>
       </c>
       <c r="E69" s="9">
         <v>90</v>
       </c>
-      <c r="F69" s="10"/>
-      <c r="G69" s="17">
+      <c r="F69" s="10">
+        <v>80.5</v>
+      </c>
+      <c r="G69" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2890,14 +3027,16 @@
       <c r="C70" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F70" s="10"/>
-      <c r="G70" s="17">
+      <c r="F70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2911,14 +3050,16 @@
       <c r="C71" s="11">
         <v>78</v>
       </c>
-      <c r="D71" s="19">
+      <c r="D71" s="18">
         <v>64</v>
       </c>
       <c r="E71" s="9">
         <v>88</v>
       </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="17">
+      <c r="F71" s="10">
+        <v>73</v>
+      </c>
+      <c r="G71" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -2932,14 +3073,16 @@
       <c r="C72" s="11">
         <v>95</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D72" s="18">
         <v>86</v>
       </c>
       <c r="E72" s="9">
         <v>19</v>
       </c>
-      <c r="F72" s="10"/>
-      <c r="G72" s="17">
+      <c r="F72" s="10">
+        <v>79.5</v>
+      </c>
+      <c r="G72" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -2953,14 +3096,16 @@
       <c r="C73" s="11">
         <v>93</v>
       </c>
-      <c r="D73" s="19">
+      <c r="D73" s="18">
         <v>79.5</v>
       </c>
       <c r="E73" s="9">
         <v>59</v>
       </c>
-      <c r="F73" s="10"/>
-      <c r="G73" s="17">
+      <c r="F73" s="10">
+        <v>86.5</v>
+      </c>
+      <c r="G73" s="16">
         <v>72.72999999999999</v>
       </c>
     </row>
@@ -2974,14 +3119,16 @@
       <c r="C74" s="11">
         <v>96</v>
       </c>
-      <c r="D74" s="19">
+      <c r="D74" s="18">
         <v>95</v>
       </c>
       <c r="E74" s="9">
         <v>90</v>
       </c>
-      <c r="F74" s="10"/>
-      <c r="G74" s="17">
+      <c r="F74" s="10">
+        <v>78</v>
+      </c>
+      <c r="G74" s="16">
         <v>93.94</v>
       </c>
     </row>
@@ -2995,14 +3142,16 @@
       <c r="C75" s="11">
         <v>98</v>
       </c>
-      <c r="D75" s="19">
+      <c r="D75" s="18">
         <v>94</v>
       </c>
       <c r="E75" s="9">
         <v>99</v>
       </c>
-      <c r="F75" s="10"/>
-      <c r="G75" s="17">
+      <c r="F75" s="10">
+        <v>81</v>
+      </c>
+      <c r="G75" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -3016,14 +3165,16 @@
       <c r="C76" s="11">
         <v>100</v>
       </c>
-      <c r="D76" s="19">
+      <c r="D76" s="18">
         <v>83</v>
       </c>
       <c r="E76" s="9">
         <v>75</v>
       </c>
-      <c r="F76" s="10"/>
-      <c r="G76" s="17">
+      <c r="F76" s="10">
+        <v>81</v>
+      </c>
+      <c r="G76" s="16">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3037,14 +3188,16 @@
       <c r="C77" s="11">
         <v>98</v>
       </c>
-      <c r="D77" s="19">
+      <c r="D77" s="18">
         <v>70</v>
       </c>
       <c r="E77" s="9">
         <v>97</v>
       </c>
-      <c r="F77" s="10"/>
-      <c r="G77" s="17">
+      <c r="F77" s="10">
+        <v>68.5</v>
+      </c>
+      <c r="G77" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3058,14 +3211,16 @@
       <c r="C78" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="D78" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F78" s="10"/>
-      <c r="G78" s="17">
+      <c r="F78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="16">
         <v>6.0600000000000005</v>
       </c>
     </row>
@@ -3079,14 +3234,16 @@
       <c r="C79" s="11">
         <v>72</v>
       </c>
-      <c r="D79" s="19">
+      <c r="D79" s="18">
         <v>84</v>
       </c>
       <c r="E79" s="9">
         <v>74</v>
       </c>
-      <c r="F79" s="10"/>
-      <c r="G79" s="17">
+      <c r="F79" s="10">
+        <v>83</v>
+      </c>
+      <c r="G79" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3100,14 +3257,16 @@
       <c r="C80" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D80" s="18" t="s">
+      <c r="D80" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F80" s="10"/>
-      <c r="G80" s="17">
+      <c r="F80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3121,14 +3280,16 @@
       <c r="C81" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F81" s="10"/>
-      <c r="G81" s="17">
+      <c r="F81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="16">
         <v>3.0300000000000002</v>
       </c>
     </row>
@@ -3142,14 +3303,16 @@
       <c r="C82" s="11">
         <v>74</v>
       </c>
-      <c r="D82" s="19">
+      <c r="D82" s="18">
         <v>79</v>
       </c>
       <c r="E82" s="9">
         <v>80</v>
       </c>
-      <c r="F82" s="10"/>
-      <c r="G82" s="17">
+      <c r="F82" s="10">
+        <v>74</v>
+      </c>
+      <c r="G82" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3163,14 +3326,16 @@
       <c r="C83" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D83" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F83" s="10"/>
-      <c r="G83" s="17">
+      <c r="F83" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3184,14 +3349,16 @@
       <c r="C84" s="11">
         <v>43</v>
       </c>
-      <c r="D84" s="19">
+      <c r="D84" s="18">
         <v>69</v>
       </c>
       <c r="E84" s="9">
         <v>84</v>
       </c>
-      <c r="F84" s="10"/>
-      <c r="G84" s="17">
+      <c r="F84" s="10">
+        <v>70</v>
+      </c>
+      <c r="G84" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -3205,14 +3372,16 @@
       <c r="C85" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D85" s="18" t="s">
+      <c r="D85" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="10"/>
-      <c r="G85" s="17">
+      <c r="F85" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3226,14 +3395,16 @@
       <c r="C86" s="11">
         <v>99</v>
       </c>
-      <c r="D86" s="19">
+      <c r="D86" s="18">
         <v>81</v>
       </c>
       <c r="E86" s="9">
         <v>59</v>
       </c>
-      <c r="F86" s="10"/>
-      <c r="G86" s="17">
+      <c r="F86" s="10">
+        <v>77</v>
+      </c>
+      <c r="G86" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3247,14 +3418,16 @@
       <c r="C87" s="11">
         <v>99</v>
       </c>
-      <c r="D87" s="19">
+      <c r="D87" s="18">
         <v>83</v>
       </c>
       <c r="E87" s="9">
         <v>69</v>
       </c>
-      <c r="F87" s="10"/>
-      <c r="G87" s="17">
+      <c r="F87" s="10">
+        <v>76.5</v>
+      </c>
+      <c r="G87" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3268,14 +3441,16 @@
       <c r="C88" s="11">
         <v>85</v>
       </c>
-      <c r="D88" s="19">
+      <c r="D88" s="18">
         <v>56</v>
       </c>
       <c r="E88" s="9">
         <v>55</v>
       </c>
-      <c r="F88" s="10"/>
-      <c r="G88" s="17">
+      <c r="F88" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G88" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -3289,14 +3464,16 @@
       <c r="C89" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D89" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="10"/>
-      <c r="G89" s="17">
+      <c r="F89" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G89" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3310,14 +3487,16 @@
       <c r="C90" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D90" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F90" s="10"/>
-      <c r="G90" s="17">
+      <c r="F90" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3331,14 +3510,16 @@
       <c r="C91" s="11">
         <v>93</v>
       </c>
-      <c r="D91" s="19">
+      <c r="D91" s="18">
         <v>67</v>
       </c>
       <c r="E91" s="9">
         <v>91</v>
       </c>
-      <c r="F91" s="10"/>
-      <c r="G91" s="17">
+      <c r="F91" s="10">
+        <v>74.5</v>
+      </c>
+      <c r="G91" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3352,14 +3533,16 @@
       <c r="C92" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="D92" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F92" s="10"/>
-      <c r="G92" s="17">
+      <c r="F92" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G92" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -3373,14 +3556,16 @@
       <c r="C93" s="11">
         <v>99</v>
       </c>
-      <c r="D93" s="19">
+      <c r="D93" s="18">
         <v>84</v>
       </c>
       <c r="E93" s="9">
         <v>68</v>
       </c>
-      <c r="F93" s="10"/>
-      <c r="G93" s="17">
+      <c r="F93" s="10">
+        <v>80</v>
+      </c>
+      <c r="G93" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3394,14 +3579,16 @@
       <c r="C94" s="11">
         <v>70</v>
       </c>
-      <c r="D94" s="19">
+      <c r="D94" s="18">
         <v>90</v>
       </c>
       <c r="E94" s="9">
         <v>86</v>
       </c>
-      <c r="F94" s="10"/>
-      <c r="G94" s="17">
+      <c r="F94" s="10">
+        <v>76</v>
+      </c>
+      <c r="G94" s="16">
         <v>96.97</v>
       </c>
     </row>
@@ -3415,14 +3602,16 @@
       <c r="C95" s="11">
         <v>90</v>
       </c>
-      <c r="D95" s="19">
+      <c r="D95" s="18">
         <v>79</v>
       </c>
       <c r="E95" s="9">
         <v>72</v>
       </c>
-      <c r="F95" s="10"/>
-      <c r="G95" s="17">
+      <c r="F95" s="10">
+        <v>83</v>
+      </c>
+      <c r="G95" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3436,14 +3625,16 @@
       <c r="C96" s="11">
         <v>82</v>
       </c>
-      <c r="D96" s="19">
+      <c r="D96" s="18">
         <v>59.5</v>
       </c>
       <c r="E96" s="9">
         <v>64</v>
       </c>
-      <c r="F96" s="10"/>
-      <c r="G96" s="17">
+      <c r="F96" s="10">
+        <v>67</v>
+      </c>
+      <c r="G96" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -3457,14 +3648,16 @@
       <c r="C97" s="11">
         <v>55</v>
       </c>
-      <c r="D97" s="18" t="s">
+      <c r="D97" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F97" s="10"/>
-      <c r="G97" s="17"/>
+      <c r="F97" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" s="16"/>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="6" t="s">
@@ -3476,14 +3669,16 @@
       <c r="C98" s="11">
         <v>100</v>
       </c>
-      <c r="D98" s="19">
+      <c r="D98" s="18">
         <v>89</v>
       </c>
       <c r="E98" s="9">
         <v>88</v>
       </c>
-      <c r="F98" s="10"/>
-      <c r="G98" s="17">
+      <c r="F98" s="10">
+        <v>75.75</v>
+      </c>
+      <c r="G98" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3497,14 +3692,16 @@
       <c r="C99" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D99" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F99" s="10"/>
-      <c r="G99" s="17">
+      <c r="F99" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G99" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3518,14 +3715,16 @@
       <c r="C100" s="11">
         <v>93</v>
       </c>
-      <c r="D100" s="19">
+      <c r="D100" s="18">
         <v>86</v>
       </c>
       <c r="E100" s="9">
         <v>73</v>
       </c>
-      <c r="F100" s="10"/>
-      <c r="G100" s="17">
+      <c r="F100" s="10">
+        <v>70</v>
+      </c>
+      <c r="G100" s="16">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3539,14 +3738,16 @@
       <c r="C101" s="11">
         <v>81</v>
       </c>
-      <c r="D101" s="19">
+      <c r="D101" s="18">
         <v>71</v>
       </c>
       <c r="E101" s="9">
         <v>55</v>
       </c>
-      <c r="F101" s="10"/>
-      <c r="G101" s="17">
+      <c r="F101" s="10">
+        <v>62.75</v>
+      </c>
+      <c r="G101" s="16">
         <v>83.33</v>
       </c>
     </row>
@@ -3560,14 +3761,16 @@
       <c r="C102" s="11">
         <v>71</v>
       </c>
-      <c r="D102" s="19">
+      <c r="D102" s="18">
         <v>55</v>
       </c>
       <c r="E102" s="9">
         <v>67</v>
       </c>
-      <c r="F102" s="10"/>
-      <c r="G102" s="17">
+      <c r="F102" s="10">
+        <v>65.5</v>
+      </c>
+      <c r="G102" s="16">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -3581,14 +3784,16 @@
       <c r="C103" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D103" s="18" t="s">
+      <c r="D103" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E103" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F103" s="10"/>
-      <c r="G103" s="17">
+      <c r="F103" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G103" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3602,14 +3807,16 @@
       <c r="C104" s="11">
         <v>85</v>
       </c>
-      <c r="D104" s="19">
+      <c r="D104" s="18">
         <v>88</v>
       </c>
       <c r="E104" s="9">
         <v>47</v>
       </c>
-      <c r="F104" s="10"/>
-      <c r="G104" s="17">
+      <c r="F104" s="10">
+        <v>76</v>
+      </c>
+      <c r="G104" s="16">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3623,14 +3830,16 @@
       <c r="C105" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="18" t="s">
+      <c r="D105" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="10"/>
-      <c r="G105" s="17">
+      <c r="F105" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105" s="16">
         <v>3.0300000000000002</v>
       </c>
     </row>
@@ -3644,14 +3853,16 @@
       <c r="C106" s="11">
         <v>71</v>
       </c>
-      <c r="D106" s="19">
+      <c r="D106" s="18">
         <v>65</v>
       </c>
       <c r="E106" s="9">
         <v>57</v>
       </c>
-      <c r="F106" s="10"/>
-      <c r="G106" s="17">
+      <c r="F106" s="10">
+        <v>67.5</v>
+      </c>
+      <c r="G106" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -3665,14 +3876,16 @@
       <c r="C107" s="11">
         <v>98</v>
       </c>
-      <c r="D107" s="19">
+      <c r="D107" s="18">
         <v>55</v>
       </c>
       <c r="E107" s="9">
         <v>85</v>
       </c>
-      <c r="F107" s="10"/>
-      <c r="G107" s="17">
+      <c r="F107" s="10">
+        <v>82</v>
+      </c>
+      <c r="G107" s="16">
         <v>78.790000000000006</v>
       </c>
     </row>
@@ -3686,14 +3899,16 @@
       <c r="C108" s="11">
         <v>83</v>
       </c>
-      <c r="D108" s="19">
+      <c r="D108" s="18">
         <v>91</v>
       </c>
       <c r="E108" s="9">
         <v>84</v>
       </c>
-      <c r="F108" s="10"/>
-      <c r="G108" s="17">
+      <c r="F108" s="10">
+        <v>83.5</v>
+      </c>
+      <c r="G108" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -3707,14 +3922,16 @@
       <c r="C109" s="11">
         <v>73</v>
       </c>
-      <c r="D109" s="19">
+      <c r="D109" s="18">
         <v>65</v>
       </c>
       <c r="E109" s="9">
         <v>63</v>
       </c>
-      <c r="F109" s="10"/>
-      <c r="G109" s="17">
+      <c r="F109" s="10">
+        <v>77</v>
+      </c>
+      <c r="G109" s="16">
         <v>87.88</v>
       </c>
     </row>
@@ -3728,14 +3945,16 @@
       <c r="C110" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D110" s="18" t="s">
+      <c r="D110" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F110" s="10"/>
-      <c r="G110" s="17">
+      <c r="F110" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G110" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3749,14 +3968,16 @@
       <c r="C111" s="11">
         <v>99</v>
       </c>
-      <c r="D111" s="19">
+      <c r="D111" s="18">
         <v>81</v>
       </c>
       <c r="E111" s="9">
         <v>68</v>
       </c>
-      <c r="F111" s="10"/>
-      <c r="G111" s="17">
+      <c r="F111" s="10">
+        <v>69.5</v>
+      </c>
+      <c r="G111" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3770,14 +3991,16 @@
       <c r="C112" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D112" s="18" t="s">
+      <c r="D112" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F112" s="10"/>
-      <c r="G112" s="17">
+      <c r="F112" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G112" s="16">
         <v>3.0300000000000002</v>
       </c>
     </row>
@@ -3791,14 +4014,16 @@
       <c r="C113" s="11">
         <v>89</v>
       </c>
-      <c r="D113" s="19">
+      <c r="D113" s="18">
         <v>87</v>
       </c>
       <c r="E113" s="9">
         <v>85</v>
       </c>
-      <c r="F113" s="10"/>
-      <c r="G113" s="17">
+      <c r="F113" s="10">
+        <v>86.25</v>
+      </c>
+      <c r="G113" s="16">
         <v>90.91</v>
       </c>
     </row>
@@ -3812,14 +4037,16 @@
       <c r="C114" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="D114" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="10"/>
-      <c r="G114" s="17">
+      <c r="F114" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G114" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3833,14 +4060,16 @@
       <c r="C115" s="11">
         <v>64</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="D115" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F115" s="10"/>
-      <c r="G115" s="17"/>
+      <c r="F115" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G115" s="16"/>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="13" t="s">
@@ -3852,14 +4081,16 @@
       <c r="C116" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D116" s="18" t="s">
+      <c r="D116" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F116" s="10"/>
-      <c r="G116" s="17">
+      <c r="F116" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G116" s="16">
         <v>12.120000000000001</v>
       </c>
     </row>
@@ -3873,14 +4104,16 @@
       <c r="C117" s="11">
         <v>61</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="D117" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F117" s="10"/>
-      <c r="G117" s="17">
+      <c r="F117" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G117" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3894,14 +4127,16 @@
       <c r="C118" s="11">
         <v>75</v>
       </c>
-      <c r="D118" s="18" t="s">
+      <c r="D118" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F118" s="10"/>
-      <c r="G118" s="17">
+      <c r="F118" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G118" s="16">
         <v>30.3</v>
       </c>
     </row>
@@ -3915,14 +4150,16 @@
       <c r="C119" s="11">
         <v>49</v>
       </c>
-      <c r="D119" s="18" t="s">
+      <c r="D119" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F119" s="10"/>
-      <c r="G119" s="17">
+      <c r="F119" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="16">
         <v>15.15</v>
       </c>
     </row>
@@ -3936,14 +4173,16 @@
       <c r="C120" s="11">
         <v>59</v>
       </c>
-      <c r="D120" s="18" t="s">
+      <c r="D120" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F120" s="10"/>
-      <c r="G120" s="17">
+      <c r="F120" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G120" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3957,14 +4196,16 @@
       <c r="C121" s="11">
         <v>47</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="D121" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F121" s="10"/>
-      <c r="G121" s="17">
+      <c r="F121" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G121" s="16">
         <v>0</v>
       </c>
     </row>
@@ -3978,14 +4219,16 @@
       <c r="C122" s="11">
         <v>61</v>
       </c>
-      <c r="D122" s="18" t="s">
+      <c r="D122" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F122" s="10"/>
-      <c r="G122" s="17">
+      <c r="F122" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G122" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -3999,14 +4242,16 @@
       <c r="C123" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D123" s="18" t="s">
+      <c r="D123" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F123" s="10"/>
-      <c r="G123" s="17">
+      <c r="F123" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G123" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4020,14 +4265,16 @@
       <c r="C124" s="11">
         <v>75</v>
       </c>
-      <c r="D124" s="18" t="s">
+      <c r="D124" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F124" s="10"/>
-      <c r="G124" s="17">
+      <c r="F124" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G124" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4041,14 +4288,16 @@
       <c r="C125" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D125" s="18" t="s">
+      <c r="D125" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F125" s="10"/>
-      <c r="G125" s="17">
+      <c r="F125" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G125" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4062,14 +4311,16 @@
       <c r="C126" s="11">
         <v>37</v>
       </c>
-      <c r="D126" s="18" t="s">
+      <c r="D126" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F126" s="10"/>
-      <c r="G126" s="17">
+      <c r="F126" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G126" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4083,14 +4334,16 @@
       <c r="C127" s="11">
         <v>79</v>
       </c>
-      <c r="D127" s="18" t="s">
+      <c r="D127" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F127" s="10"/>
-      <c r="G127" s="17">
+      <c r="F127" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G127" s="16">
         <v>15.15</v>
       </c>
     </row>
@@ -4104,14 +4357,16 @@
       <c r="C128" s="11">
         <v>62</v>
       </c>
-      <c r="D128" s="18" t="s">
+      <c r="D128" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F128" s="10"/>
-      <c r="G128" s="17">
+      <c r="F128" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G128" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4125,14 +4380,16 @@
       <c r="C129" s="11">
         <v>67</v>
       </c>
-      <c r="D129" s="19">
+      <c r="D129" s="18">
         <v>59</v>
       </c>
       <c r="E129" s="9">
         <v>62</v>
       </c>
-      <c r="F129" s="10"/>
-      <c r="G129" s="17">
+      <c r="F129" s="10">
+        <v>59</v>
+      </c>
+      <c r="G129" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -4146,14 +4403,16 @@
       <c r="C130" s="11">
         <v>99</v>
       </c>
-      <c r="D130" s="18" t="s">
+      <c r="D130" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F130" s="10"/>
-      <c r="G130" s="17">
+      <c r="F130" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G130" s="16">
         <v>21.21</v>
       </c>
     </row>
@@ -4167,14 +4426,16 @@
       <c r="C131" s="11">
         <v>85</v>
       </c>
-      <c r="D131" s="18" t="s">
+      <c r="D131" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F131" s="10"/>
-      <c r="G131" s="17">
+      <c r="F131" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G131" s="16">
         <v>9.09</v>
       </c>
     </row>
@@ -4188,14 +4449,16 @@
       <c r="C132" s="11">
         <v>48</v>
       </c>
-      <c r="D132" s="19">
+      <c r="D132" s="18">
         <v>31</v>
       </c>
       <c r="E132" s="9">
         <v>38</v>
       </c>
-      <c r="F132" s="10"/>
-      <c r="G132" s="17">
+      <c r="F132" s="10">
+        <v>69.25</v>
+      </c>
+      <c r="G132" s="16">
         <v>75.760000000000005</v>
       </c>
     </row>
@@ -4209,14 +4472,16 @@
       <c r="C133" s="11">
         <v>55</v>
       </c>
-      <c r="D133" s="18" t="s">
+      <c r="D133" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F133" s="10"/>
-      <c r="G133" s="17">
+      <c r="F133" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G133" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4230,14 +4495,16 @@
       <c r="C134" s="11">
         <v>72</v>
       </c>
-      <c r="D134" s="19">
+      <c r="D134" s="18">
         <v>54</v>
       </c>
       <c r="E134" s="9">
         <v>47</v>
       </c>
-      <c r="F134" s="10"/>
-      <c r="G134" s="17">
+      <c r="F134" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G134" s="16">
         <v>84.850000000000009</v>
       </c>
     </row>
@@ -4251,14 +4518,16 @@
       <c r="C135" s="11">
         <v>77</v>
       </c>
-      <c r="D135" s="18" t="s">
+      <c r="D135" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="10"/>
-      <c r="G135" s="17">
+      <c r="F135" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G135" s="16">
         <v>15.15</v>
       </c>
     </row>
@@ -4272,14 +4541,16 @@
       <c r="C136" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D136" s="18" t="s">
+      <c r="D136" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F136" s="10"/>
-      <c r="G136" s="17">
+      <c r="F136" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G136" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4293,14 +4564,16 @@
       <c r="C137" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D137" s="18" t="s">
+      <c r="D137" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F137" s="10"/>
-      <c r="G137" s="17">
+      <c r="F137" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G137" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4314,14 +4587,16 @@
       <c r="C138" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D138" s="18" t="s">
+      <c r="D138" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F138" s="10"/>
-      <c r="G138" s="17">
+      <c r="F138" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G138" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4335,14 +4610,16 @@
       <c r="C139" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D139" s="18" t="s">
+      <c r="D139" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F139" s="10"/>
-      <c r="G139" s="17">
+      <c r="F139" s="10">
+        <v>31.5</v>
+      </c>
+      <c r="G139" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4356,14 +4633,16 @@
       <c r="C140" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D140" s="18" t="s">
+      <c r="D140" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F140" s="10"/>
-      <c r="G140" s="17">
+      <c r="F140" s="10">
+        <v>35.75</v>
+      </c>
+      <c r="G140" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4377,14 +4656,16 @@
       <c r="C141" s="11">
         <v>59</v>
       </c>
-      <c r="D141" s="18" t="s">
+      <c r="D141" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F141" s="10"/>
-      <c r="G141" s="17">
+      <c r="F141" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G141" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4395,17 +4676,19 @@
       <c r="B142" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C142" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" s="19">
+      <c r="C142" s="8">
+        <v>95</v>
+      </c>
+      <c r="D142" s="18">
         <v>73</v>
       </c>
       <c r="E142" s="9">
         <v>98</v>
       </c>
-      <c r="F142" s="10"/>
-      <c r="G142" s="17">
+      <c r="F142" s="10">
+        <v>78.5</v>
+      </c>
+      <c r="G142" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4419,14 +4702,16 @@
       <c r="C143" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D143" s="18" t="s">
+      <c r="D143" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="10"/>
-      <c r="G143" s="17">
+      <c r="F143" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G143" s="16">
         <v>18.18</v>
       </c>
     </row>
@@ -4440,14 +4725,16 @@
       <c r="C144" s="11">
         <v>48</v>
       </c>
-      <c r="D144" s="18" t="s">
+      <c r="D144" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F144" s="10"/>
-      <c r="G144" s="17">
+      <c r="F144" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G144" s="16">
         <v>51.519999999999996</v>
       </c>
     </row>
@@ -4461,18 +4748,21 @@
       <c r="C145" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D145" s="18" t="s">
+      <c r="D145" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F145" s="16"/>
-      <c r="G145" s="17">
+      <c r="F145" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G145" s="16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>